--- a/combined_metrics.xlsx
+++ b/combined_metrics.xlsx
@@ -1,27 +1,41 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29628"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr defaultThemeVersion="202300"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\elena\Documents\GitHub\tei_ner\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:9_{3B17A165-4E19-4510-8A7D-01F59604F541}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6AE1CC0-D24F-40D5-9F7D-C772C89A167E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{A8BB7F58-4C6E-49D6-95EE-AF11280C5AAB}"/>
+    <workbookView xWindow="38280" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="1" xr2:uid="{A8BB7F58-4C6E-49D6-95EE-AF11280C5AAB}"/>
   </bookViews>
   <sheets>
     <sheet name="combined_metrics" sheetId="1" r:id="rId1"/>
-    <sheet name="averages" sheetId="2" r:id="rId2"/>
+    <sheet name="post-dapt" sheetId="3" r:id="rId2"/>
+    <sheet name="averages" sheetId="2" r:id="rId3"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1027" uniqueCount="635">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1161" uniqueCount="659">
   <si>
     <t>timestamp</t>
   </si>
@@ -1926,6 +1940,78 @@
   </si>
   <si>
     <t>mean</t>
+  </si>
+  <si>
+    <t>precision</t>
+  </si>
+  <si>
+    <t>recall</t>
+  </si>
+  <si>
+    <t>f1</t>
+  </si>
+  <si>
+    <t>epoch</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/xlmr_large_dapt/final</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/model_roberta_large_dapt_42_1e5/checkpoint-800</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/model_roberta_large_dapt_43_1e5/checkpoint-800</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/model_roberta_large_dapt_44_1e5/checkpoint-800</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/model_roberta_large_dapt_45_1e5/checkpoint-800</t>
+  </si>
+  <si>
+    <t>2026-03-06T11:06:31.214039</t>
+  </si>
+  <si>
+    <t>/content/drive/MyDrive/ner_tei/hf_dataset</t>
+  </si>
+  <si>
+    <t>0.4932642487046632</t>
+  </si>
+  <si>
+    <t>0.5982130765914917</t>
+  </si>
+  <si>
+    <t>0.5319024324417114</t>
+  </si>
+  <si>
+    <t>2026-03-06T11:25:43.878703</t>
+  </si>
+  <si>
+    <t>0.48757255543979755</t>
+  </si>
+  <si>
+    <t>0.5553594827651978</t>
+  </si>
+  <si>
+    <t>2026-03-06T14:34:32.384920</t>
+  </si>
+  <si>
+    <t>0.4936521995866549</t>
+  </si>
+  <si>
+    <t>0.6451340913772583</t>
+  </si>
+  <si>
+    <t>0.5118981003761292</t>
+  </si>
+  <si>
+    <t>2026-03-06T15:15:20.414614</t>
+  </si>
+  <si>
+    <t>0.5021745433458974</t>
+  </si>
+  <si>
+    <t>0.5126075148582458</t>
   </si>
 </sst>
 </file>
@@ -2423,13 +2509,13 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="center"/>
-    </xf>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" quotePrefix="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
     <xf numFmtId="164" fontId="0" fillId="33" borderId="0" xfId="0" quotePrefix="1" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -2817,7 +2903,7 @@
     <col min="15" max="15" width="13.53125" customWidth="1"/>
     <col min="16" max="16" width="24.6640625" customWidth="1"/>
     <col min="17" max="17" width="10.265625" style="2" bestFit="1" customWidth="1"/>
-    <col min="25" max="25" width="19.73046875" style="5" customWidth="1"/>
+    <col min="25" max="25" width="19.73046875" style="4" customWidth="1"/>
     <col min="26" max="26" width="20.265625" customWidth="1"/>
     <col min="27" max="27" width="19.19921875" customWidth="1"/>
     <col min="28" max="28" width="21.06640625" customWidth="1"/>
@@ -2825,7 +2911,7 @@
     <col min="30" max="30" width="24.3984375" customWidth="1"/>
     <col min="31" max="31" width="22.6640625" customWidth="1"/>
     <col min="32" max="32" width="19.86328125" customWidth="1"/>
-    <col min="33" max="33" width="22" style="5" customWidth="1"/>
+    <col min="33" max="33" width="22" style="4" customWidth="1"/>
     <col min="34" max="34" width="23.46484375" customWidth="1"/>
     <col min="35" max="35" width="16.3984375" customWidth="1"/>
     <col min="36" max="36" width="18" customWidth="1"/>
@@ -2909,7 +2995,7 @@
       <c r="X1" t="s">
         <v>22</v>
       </c>
-      <c r="Y1" s="5" t="s">
+      <c r="Y1" s="4" t="s">
         <v>23</v>
       </c>
       <c r="Z1" t="s">
@@ -2933,7 +3019,7 @@
       <c r="AF1" t="s">
         <v>30</v>
       </c>
-      <c r="AG1" s="5" t="s">
+      <c r="AG1" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AH1" t="s">
@@ -3040,7 +3126,7 @@
       <c r="X2" s="1" t="s">
         <v>53</v>
       </c>
-      <c r="Y2" s="5">
+      <c r="Y2" s="4">
         <v>0.51247248716067495</v>
       </c>
       <c r="Z2" s="1">
@@ -3064,7 +3150,7 @@
       <c r="AF2" s="1">
         <v>0.58888888888888802</v>
       </c>
-      <c r="AG2" s="5">
+      <c r="AG2" s="4">
         <v>0.39120694483337998</v>
       </c>
       <c r="AH2" s="1">
@@ -3171,7 +3257,7 @@
       <c r="X3" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="Y3" s="5">
+      <c r="Y3" s="4">
         <v>0.56563398275311405</v>
       </c>
       <c r="Z3" s="1">
@@ -3195,7 +3281,7 @@
       <c r="AF3" s="1">
         <v>0.736363636363636</v>
       </c>
-      <c r="AG3" s="6" t="s">
+      <c r="AG3" s="5" t="s">
         <v>73</v>
       </c>
       <c r="AH3" s="1">
@@ -3302,7 +3388,7 @@
       <c r="X4" s="1" t="s">
         <v>92</v>
       </c>
-      <c r="Y4" s="6" t="s">
+      <c r="Y4" s="5" t="s">
         <v>93</v>
       </c>
       <c r="Z4" s="1">
@@ -3326,7 +3412,7 @@
       <c r="AF4">
         <v>0.6</v>
       </c>
-      <c r="AG4" s="5">
+      <c r="AG4" s="4">
         <v>0.46121534584150098</v>
       </c>
       <c r="AH4" s="1">
@@ -3433,7 +3519,7 @@
       <c r="X5" s="1" t="s">
         <v>114</v>
       </c>
-      <c r="Y5" s="6" t="s">
+      <c r="Y5" s="5" t="s">
         <v>115</v>
       </c>
       <c r="Z5" s="1">
@@ -3457,7 +3543,7 @@
       <c r="AF5" s="1">
         <v>0.74672489082969395</v>
       </c>
-      <c r="AG5" s="6" t="s">
+      <c r="AG5" s="5" t="s">
         <v>116</v>
       </c>
       <c r="AH5" s="1">
@@ -3564,7 +3650,7 @@
       <c r="X6" s="1" t="s">
         <v>133</v>
       </c>
-      <c r="Y6" s="6" t="s">
+      <c r="Y6" s="5" t="s">
         <v>134</v>
       </c>
       <c r="Z6" s="1">
@@ -3588,7 +3674,7 @@
       <c r="AF6" s="1">
         <v>0.57360406091370497</v>
       </c>
-      <c r="AG6" s="6" t="s">
+      <c r="AG6" s="5" t="s">
         <v>135</v>
       </c>
       <c r="AH6" s="1">
@@ -3695,7 +3781,7 @@
       <c r="X7" s="1" t="s">
         <v>154</v>
       </c>
-      <c r="Y7" s="5">
+      <c r="Y7" s="4">
         <v>0.58530544854155198</v>
       </c>
       <c r="Z7" s="1">
@@ -3719,7 +3805,7 @@
       <c r="AF7" s="1">
         <v>0.74782608695652097</v>
       </c>
-      <c r="AG7" s="6" t="s">
+      <c r="AG7" s="5" t="s">
         <v>155</v>
       </c>
       <c r="AH7" s="1">
@@ -3826,7 +3912,7 @@
       <c r="X8">
         <v>0.58563535911602205</v>
       </c>
-      <c r="Y8" s="6" t="s">
+      <c r="Y8" s="5" t="s">
         <v>62</v>
       </c>
       <c r="Z8" s="1">
@@ -3850,7 +3936,7 @@
       <c r="AF8" s="1">
         <v>0.59550561797752799</v>
       </c>
-      <c r="AG8" s="6" t="s">
+      <c r="AG8" s="5" t="s">
         <v>63</v>
       </c>
       <c r="AH8" s="1">
@@ -3957,7 +4043,7 @@
       <c r="X9" s="1" t="s">
         <v>81</v>
       </c>
-      <c r="Y9" s="5">
+      <c r="Y9" s="4">
         <v>0.55188541362174803</v>
       </c>
       <c r="Z9">
@@ -3981,7 +4067,7 @@
       <c r="AF9" s="1">
         <v>0.74770642201834803</v>
       </c>
-      <c r="AG9" s="6" t="s">
+      <c r="AG9" s="5" t="s">
         <v>82</v>
       </c>
       <c r="AH9" s="1">
@@ -4088,7 +4174,7 @@
       <c r="X10" s="1" t="s">
         <v>104</v>
       </c>
-      <c r="Y10" s="6" t="s">
+      <c r="Y10" s="5" t="s">
         <v>105</v>
       </c>
       <c r="Z10" s="1">
@@ -4112,7 +4198,7 @@
       <c r="AF10">
         <v>0.578125</v>
       </c>
-      <c r="AG10" s="6" t="s">
+      <c r="AG10" s="5" t="s">
         <v>106</v>
       </c>
       <c r="AH10" s="1">
@@ -4219,7 +4305,7 @@
       <c r="X11" s="1" t="s">
         <v>121</v>
       </c>
-      <c r="Y11" s="6" t="s">
+      <c r="Y11" s="5" t="s">
         <v>122</v>
       </c>
       <c r="Z11">
@@ -4243,7 +4329,7 @@
       <c r="AF11" s="1">
         <v>0.72807017543859598</v>
       </c>
-      <c r="AG11" s="6" t="s">
+      <c r="AG11" s="5" t="s">
         <v>123</v>
       </c>
       <c r="AH11" s="1">
@@ -4350,7 +4436,7 @@
       <c r="X12" s="1" t="s">
         <v>144</v>
       </c>
-      <c r="Y12" s="6" t="s">
+      <c r="Y12" s="5" t="s">
         <v>145</v>
       </c>
       <c r="Z12" s="1">
@@ -4374,7 +4460,7 @@
       <c r="AF12" s="1">
         <v>0.56544502617800996</v>
       </c>
-      <c r="AG12" s="6" t="s">
+      <c r="AG12" s="5" t="s">
         <v>146</v>
       </c>
       <c r="AH12" s="1">
@@ -4481,7 +4567,7 @@
       <c r="X13">
         <v>0.71186440677966101</v>
       </c>
-      <c r="Y13" s="6" t="s">
+      <c r="Y13" s="5" t="s">
         <v>163</v>
       </c>
       <c r="Z13">
@@ -4505,7 +4591,7 @@
       <c r="AF13">
         <v>0.71186440677966101</v>
       </c>
-      <c r="AG13" s="6" t="s">
+      <c r="AG13" s="5" t="s">
         <v>164</v>
       </c>
       <c r="AH13" s="1">
@@ -4612,7 +4698,7 @@
       <c r="X14">
         <v>0.55585831062670299</v>
       </c>
-      <c r="Y14" s="6" t="s">
+      <c r="Y14" s="5" t="s">
         <v>174</v>
       </c>
       <c r="Z14" s="1">
@@ -4636,7 +4722,7 @@
       <c r="AF14" s="1">
         <v>0.55434782608695599</v>
       </c>
-      <c r="AG14" s="6" t="s">
+      <c r="AG14" s="5" t="s">
         <v>175</v>
       </c>
       <c r="AH14" s="1">
@@ -4743,7 +4829,7 @@
       <c r="X15">
         <v>0.64978902953586504</v>
       </c>
-      <c r="Y15" s="6" t="s">
+      <c r="Y15" s="5" t="s">
         <v>192</v>
       </c>
       <c r="Z15">
@@ -4767,7 +4853,7 @@
       <c r="AF15">
         <v>0.65254237288135597</v>
       </c>
-      <c r="AG15" s="6" t="s">
+      <c r="AG15" s="5" t="s">
         <v>194</v>
       </c>
       <c r="AH15" s="1">
@@ -4874,7 +4960,7 @@
       <c r="X16" s="1" t="s">
         <v>212</v>
       </c>
-      <c r="Y16" s="6" t="s">
+      <c r="Y16" s="5" t="s">
         <v>213</v>
       </c>
       <c r="Z16">
@@ -4898,7 +4984,7 @@
       <c r="AF16">
         <v>0.52682926829268295</v>
       </c>
-      <c r="AG16" s="5">
+      <c r="AG16" s="4">
         <v>0.48104465037910699</v>
       </c>
       <c r="AH16" s="1">
@@ -5005,7 +5091,7 @@
       <c r="X17" s="1" t="s">
         <v>229</v>
       </c>
-      <c r="Y17" s="6" t="s">
+      <c r="Y17" s="5" t="s">
         <v>230</v>
       </c>
       <c r="Z17">
@@ -5029,7 +5115,7 @@
       <c r="AF17" s="1">
         <v>0.69512195121951204</v>
       </c>
-      <c r="AG17" s="6" t="s">
+      <c r="AG17" s="5" t="s">
         <v>231</v>
       </c>
       <c r="AH17" s="1">
@@ -5136,7 +5222,7 @@
       <c r="X18" s="1" t="s">
         <v>251</v>
       </c>
-      <c r="Y18" s="6" t="s">
+      <c r="Y18" s="5" t="s">
         <v>252</v>
       </c>
       <c r="Z18" s="1">
@@ -5160,7 +5246,7 @@
       <c r="AF18">
         <v>0.56499999999999995</v>
       </c>
-      <c r="AG18" s="5">
+      <c r="AG18" s="4">
         <v>0.50772254984554899</v>
       </c>
       <c r="AH18">
@@ -5267,7 +5353,7 @@
       <c r="X19" s="1" t="s">
         <v>271</v>
       </c>
-      <c r="Y19" s="6" t="s">
+      <c r="Y19" s="5" t="s">
         <v>272</v>
       </c>
       <c r="Z19" s="1">
@@ -5291,7 +5377,7 @@
       <c r="AF19" s="1">
         <v>0.71659919028340002</v>
       </c>
-      <c r="AG19" s="6" t="s">
+      <c r="AG19" s="5" t="s">
         <v>273</v>
       </c>
       <c r="AH19" s="1">
@@ -5398,7 +5484,7 @@
       <c r="X20" s="1" t="s">
         <v>184</v>
       </c>
-      <c r="Y20" s="6" t="s">
+      <c r="Y20" s="5" t="s">
         <v>185</v>
       </c>
       <c r="Z20" s="1">
@@ -5422,7 +5508,7 @@
       <c r="AF20" s="1">
         <v>0.57714285714285696</v>
       </c>
-      <c r="AG20" s="6" t="s">
+      <c r="AG20" s="5" t="s">
         <v>187</v>
       </c>
       <c r="AH20" s="1">
@@ -5529,7 +5615,7 @@
       <c r="X21" s="1" t="s">
         <v>201</v>
       </c>
-      <c r="Y21" s="6" t="s">
+      <c r="Y21" s="5" t="s">
         <v>202</v>
       </c>
       <c r="Z21" s="1">
@@ -5553,7 +5639,7 @@
       <c r="AF21" s="1">
         <v>0.706666666666666</v>
       </c>
-      <c r="AG21" s="6" t="s">
+      <c r="AG21" s="5" t="s">
         <v>203</v>
       </c>
       <c r="AH21" s="1">
@@ -5660,7 +5746,7 @@
       <c r="X22">
         <v>0.579088471849866</v>
       </c>
-      <c r="Y22" s="5">
+      <c r="Y22" s="4">
         <v>0.50165912518853695</v>
       </c>
       <c r="Z22" s="1">
@@ -5684,7 +5770,7 @@
       <c r="AF22" s="1">
         <v>0.56842105263157805</v>
       </c>
-      <c r="AG22" s="5">
+      <c r="AG22" s="4">
         <v>0.46700365065992699</v>
       </c>
       <c r="AH22" s="1">
@@ -5791,7 +5877,7 @@
       <c r="X23" s="1" t="s">
         <v>239</v>
       </c>
-      <c r="Y23" s="6" t="s">
+      <c r="Y23" s="5" t="s">
         <v>240</v>
       </c>
       <c r="Z23" s="1">
@@ -5815,7 +5901,7 @@
       <c r="AF23" s="1">
         <v>0.74583333333333302</v>
       </c>
-      <c r="AG23" s="6" t="s">
+      <c r="AG23" s="5" t="s">
         <v>241</v>
       </c>
       <c r="AH23" s="1">
@@ -5922,7 +6008,7 @@
       <c r="X24" s="1" t="s">
         <v>262</v>
       </c>
-      <c r="Y24" s="5">
+      <c r="Y24" s="4">
         <v>0.50774627301958497</v>
       </c>
       <c r="Z24" s="1">
@@ -5946,7 +6032,7 @@
       <c r="AF24">
         <v>0.56000000000000005</v>
       </c>
-      <c r="AG24" s="6" t="s">
+      <c r="AG24" s="5" t="s">
         <v>263</v>
       </c>
       <c r="AH24" s="1">
@@ -6053,7 +6139,7 @@
       <c r="X25" s="1" t="s">
         <v>279</v>
       </c>
-      <c r="Y25" s="6" t="s">
+      <c r="Y25" s="5" t="s">
         <v>280</v>
       </c>
       <c r="Z25" s="1">
@@ -6077,7 +6163,7 @@
       <c r="AF25" s="1">
         <v>0.74273858921161795</v>
       </c>
-      <c r="AG25" s="6" t="s">
+      <c r="AG25" s="5" t="s">
         <v>281</v>
       </c>
       <c r="AH25" s="1">
@@ -6184,7 +6270,7 @@
       <c r="X26" s="1" t="s">
         <v>292</v>
       </c>
-      <c r="Y26" s="6" t="s">
+      <c r="Y26" s="5" t="s">
         <v>293</v>
       </c>
       <c r="Z26" s="1">
@@ -6208,7 +6294,7 @@
       <c r="AF26">
         <v>0.63157894736842102</v>
       </c>
-      <c r="AG26" s="6" t="s">
+      <c r="AG26" s="5" t="s">
         <v>294</v>
       </c>
       <c r="AH26" s="1">
@@ -6315,7 +6401,7 @@
       <c r="X27" s="1" t="s">
         <v>54</v>
       </c>
-      <c r="Y27" s="6" t="s">
+      <c r="Y27" s="5" t="s">
         <v>310</v>
       </c>
       <c r="Z27" s="1">
@@ -6339,7 +6425,7 @@
       <c r="AF27">
         <v>0.69585253456221197</v>
       </c>
-      <c r="AG27" s="6" t="s">
+      <c r="AG27" s="5" t="s">
         <v>311</v>
       </c>
       <c r="AH27" s="1">
@@ -6446,7 +6532,7 @@
       <c r="X28">
         <v>0.58689458689458696</v>
       </c>
-      <c r="Y28" s="6" t="s">
+      <c r="Y28" s="5" t="s">
         <v>328</v>
       </c>
       <c r="Z28" s="1">
@@ -6470,7 +6556,7 @@
       <c r="AF28" s="1">
         <v>0.61676646706586802</v>
       </c>
-      <c r="AG28" s="6" t="s">
+      <c r="AG28" s="5" t="s">
         <v>330</v>
       </c>
       <c r="AH28" s="1">
@@ -6577,7 +6663,7 @@
       <c r="X29" s="1" t="s">
         <v>345</v>
       </c>
-      <c r="Y29" s="6" t="s">
+      <c r="Y29" s="5" t="s">
         <v>346</v>
       </c>
       <c r="Z29">
@@ -6601,7 +6687,7 @@
       <c r="AF29" s="1">
         <v>0.73148148148148096</v>
       </c>
-      <c r="AG29" s="6" t="s">
+      <c r="AG29" s="5" t="s">
         <v>347</v>
       </c>
       <c r="AH29" s="1">
@@ -6708,7 +6794,7 @@
       <c r="X30" s="1" t="s">
         <v>365</v>
       </c>
-      <c r="Y30" s="6" t="s">
+      <c r="Y30" s="5" t="s">
         <v>366</v>
       </c>
       <c r="Z30" s="1">
@@ -6732,7 +6818,7 @@
       <c r="AF30" s="1">
         <v>0.63030303030303003</v>
       </c>
-      <c r="AG30" s="6" t="s">
+      <c r="AG30" s="5" t="s">
         <v>367</v>
       </c>
       <c r="AH30" s="1">
@@ -6839,7 +6925,7 @@
       <c r="X31" s="1" t="s">
         <v>385</v>
       </c>
-      <c r="Y31" s="6" t="s">
+      <c r="Y31" s="5" t="s">
         <v>386</v>
       </c>
       <c r="Z31" s="1">
@@ -6863,7 +6949,7 @@
       <c r="AF31" s="1">
         <v>0.74056603773584895</v>
       </c>
-      <c r="AG31" s="6" t="s">
+      <c r="AG31" s="5" t="s">
         <v>387</v>
       </c>
       <c r="AH31" s="1">
@@ -6970,7 +7056,7 @@
       <c r="X32" s="1" t="s">
         <v>303</v>
       </c>
-      <c r="Y32" s="5">
+      <c r="Y32" s="4">
         <v>0.46270883054892598</v>
       </c>
       <c r="Z32" s="1">
@@ -6994,7 +7080,7 @@
       <c r="AF32" s="1">
         <v>0.63354037267080698</v>
       </c>
-      <c r="AG32" s="6" t="s">
+      <c r="AG32" s="5" t="s">
         <v>304</v>
       </c>
       <c r="AH32" s="1">
@@ -7101,7 +7187,7 @@
       <c r="X33" s="1" t="s">
         <v>319</v>
       </c>
-      <c r="Y33" s="5">
+      <c r="Y33" s="4">
         <v>0.54190871369294602</v>
       </c>
       <c r="Z33" s="1">
@@ -7125,7 +7211,7 @@
       <c r="AF33" s="1">
         <v>0.74752475247524697</v>
       </c>
-      <c r="AG33" s="6" t="s">
+      <c r="AG33" s="5" t="s">
         <v>320</v>
       </c>
       <c r="AH33" s="1">
@@ -7232,7 +7318,7 @@
       <c r="X34" s="1" t="s">
         <v>338</v>
       </c>
-      <c r="Y34" s="6" t="s">
+      <c r="Y34" s="5" t="s">
         <v>339</v>
       </c>
       <c r="Z34">
@@ -7256,7 +7342,7 @@
       <c r="AF34" s="1">
         <v>0.63687150837988804</v>
       </c>
-      <c r="AG34" s="6" t="s">
+      <c r="AG34" s="5" t="s">
         <v>341</v>
       </c>
       <c r="AH34" s="1">
@@ -7363,7 +7449,7 @@
       <c r="X35" s="1" t="s">
         <v>355</v>
       </c>
-      <c r="Y35" s="6" t="s">
+      <c r="Y35" s="5" t="s">
         <v>356</v>
       </c>
       <c r="Z35" s="1">
@@ -7387,7 +7473,7 @@
       <c r="AF35" s="1">
         <v>0.723981900452488</v>
       </c>
-      <c r="AG35" s="6" t="s">
+      <c r="AG35" s="5" t="s">
         <v>123</v>
       </c>
       <c r="AH35" s="1">
@@ -7494,7 +7580,7 @@
       <c r="X36" s="1" t="s">
         <v>375</v>
       </c>
-      <c r="Y36" s="6" t="s">
+      <c r="Y36" s="5" t="s">
         <v>376</v>
       </c>
       <c r="Z36" s="1">
@@ -7518,7 +7604,7 @@
       <c r="AF36" s="1">
         <v>0.64130434782608603</v>
       </c>
-      <c r="AG36" s="6" t="s">
+      <c r="AG36" s="5" t="s">
         <v>377</v>
       </c>
       <c r="AH36" s="1">
@@ -7625,7 +7711,7 @@
       <c r="X37" s="1" t="s">
         <v>393</v>
       </c>
-      <c r="Y37" s="6" t="s">
+      <c r="Y37" s="5" t="s">
         <v>394</v>
       </c>
       <c r="Z37" s="1">
@@ -7649,7 +7735,7 @@
       <c r="AF37" s="1">
         <v>0.73913043478260798</v>
       </c>
-      <c r="AG37" s="6" t="s">
+      <c r="AG37" s="5" t="s">
         <v>395</v>
       </c>
       <c r="AH37" s="1">
@@ -7756,7 +7842,7 @@
       <c r="X38" s="1" t="s">
         <v>404</v>
       </c>
-      <c r="Y38" s="6" t="s">
+      <c r="Y38" s="5" t="s">
         <v>405</v>
       </c>
       <c r="Z38" s="1">
@@ -7780,7 +7866,7 @@
       <c r="AF38" s="1">
         <v>0.61290322580645096</v>
       </c>
-      <c r="AG38" s="6" t="s">
+      <c r="AG38" s="5" t="s">
         <v>406</v>
       </c>
       <c r="AH38" s="1">
@@ -7887,7 +7973,7 @@
       <c r="X39">
         <v>0.69107551487414198</v>
       </c>
-      <c r="Y39" s="6" t="s">
+      <c r="Y39" s="5" t="s">
         <v>421</v>
       </c>
       <c r="Z39" s="1">
@@ -7911,7 +7997,7 @@
       <c r="AF39">
         <v>0.755</v>
       </c>
-      <c r="AG39" s="6" t="s">
+      <c r="AG39" s="5" t="s">
         <v>422</v>
       </c>
       <c r="AH39" s="1">
@@ -8018,7 +8104,7 @@
       <c r="X40" s="1" t="s">
         <v>439</v>
       </c>
-      <c r="Y40" s="6" t="s">
+      <c r="Y40" s="5" t="s">
         <v>440</v>
       </c>
       <c r="Z40" s="1">
@@ -8042,7 +8128,7 @@
       <c r="AF40" s="1">
         <v>0.60638297872340396</v>
       </c>
-      <c r="AG40" s="6" t="s">
+      <c r="AG40" s="5" t="s">
         <v>441</v>
       </c>
       <c r="AH40" s="1">
@@ -8149,7 +8235,7 @@
       <c r="X41" s="1" t="s">
         <v>457</v>
       </c>
-      <c r="Y41" s="6" t="s">
+      <c r="Y41" s="5" t="s">
         <v>458</v>
       </c>
       <c r="Z41" s="1">
@@ -8173,7 +8259,7 @@
       <c r="AF41" s="1">
         <v>0.74666666666666603</v>
       </c>
-      <c r="AG41" s="6" t="s">
+      <c r="AG41" s="5" t="s">
         <v>459</v>
       </c>
       <c r="AH41" s="1">
@@ -8280,7 +8366,7 @@
       <c r="X42" s="1" t="s">
         <v>478</v>
       </c>
-      <c r="Y42" s="6" t="s">
+      <c r="Y42" s="5" t="s">
         <v>479</v>
       </c>
       <c r="Z42" s="1">
@@ -8304,7 +8390,7 @@
       <c r="AF42" s="1">
         <v>0.60540540540540499</v>
       </c>
-      <c r="AG42" s="6" t="s">
+      <c r="AG42" s="5" t="s">
         <v>481</v>
       </c>
       <c r="AH42" s="1">
@@ -8411,7 +8497,7 @@
       <c r="X43" s="1" t="s">
         <v>500</v>
       </c>
-      <c r="Y43" s="6" t="s">
+      <c r="Y43" s="5" t="s">
         <v>501</v>
       </c>
       <c r="Z43" s="1">
@@ -8435,7 +8521,7 @@
       <c r="AF43" s="1">
         <v>0.740088105726872</v>
       </c>
-      <c r="AG43" s="6" t="s">
+      <c r="AG43" s="5" t="s">
         <v>502</v>
       </c>
       <c r="AH43" s="1">
@@ -8542,7 +8628,7 @@
       <c r="X44" s="1" t="s">
         <v>413</v>
       </c>
-      <c r="Y44" s="6" t="s">
+      <c r="Y44" s="5" t="s">
         <v>414</v>
       </c>
       <c r="Z44" s="1">
@@ -8566,7 +8652,7 @@
       <c r="AF44" s="1">
         <v>0.61309523809523803</v>
       </c>
-      <c r="AG44" s="6" t="s">
+      <c r="AG44" s="5" t="s">
         <v>415</v>
       </c>
       <c r="AH44" s="1">
@@ -8673,7 +8759,7 @@
       <c r="X45" s="1" t="s">
         <v>427</v>
       </c>
-      <c r="Y45" s="6" t="s">
+      <c r="Y45" s="5" t="s">
         <v>428</v>
       </c>
       <c r="Z45" s="1">
@@ -8697,7 +8783,7 @@
       <c r="AF45" s="1">
         <v>0.75728155339805803</v>
       </c>
-      <c r="AG45" s="6" t="s">
+      <c r="AG45" s="5" t="s">
         <v>429</v>
       </c>
       <c r="AH45" s="1">
@@ -8804,7 +8890,7 @@
       <c r="X46">
         <v>0.59640102827763497</v>
       </c>
-      <c r="Y46" s="6" t="s">
+      <c r="Y46" s="5" t="s">
         <v>450</v>
       </c>
       <c r="Z46" s="1">
@@ -8828,7 +8914,7 @@
       <c r="AF46" s="1">
         <v>0.56585365853658498</v>
       </c>
-      <c r="AG46" s="5">
+      <c r="AG46" s="4">
         <v>0.482421875</v>
       </c>
       <c r="AH46" s="1">
@@ -8935,7 +9021,7 @@
       <c r="X47">
         <v>0.72340425531914898</v>
       </c>
-      <c r="Y47" s="6" t="s">
+      <c r="Y47" s="5" t="s">
         <v>465</v>
       </c>
       <c r="Z47" s="1">
@@ -8959,7 +9045,7 @@
       <c r="AF47" s="1">
         <v>0.72961373390557904</v>
       </c>
-      <c r="AG47" s="6" t="s">
+      <c r="AG47" s="5" t="s">
         <v>467</v>
       </c>
       <c r="AH47" s="1">
@@ -9066,7 +9152,7 @@
       <c r="X48" s="1" t="s">
         <v>489</v>
       </c>
-      <c r="Y48" s="6" t="s">
+      <c r="Y48" s="5" t="s">
         <v>490</v>
       </c>
       <c r="Z48" s="1">
@@ -9090,7 +9176,7 @@
       <c r="AF48" s="1">
         <v>0.58333333333333304</v>
       </c>
-      <c r="AG48" s="6" t="s">
+      <c r="AG48" s="5" t="s">
         <v>492</v>
       </c>
       <c r="AH48" s="1">
@@ -9197,7 +9283,7 @@
       <c r="X49" s="1" t="s">
         <v>466</v>
       </c>
-      <c r="Y49" s="6" t="s">
+      <c r="Y49" s="5" t="s">
         <v>510</v>
       </c>
       <c r="Z49">
@@ -9221,7 +9307,7 @@
       <c r="AF49">
         <v>0.74235807860262004</v>
       </c>
-      <c r="AG49" s="5">
+      <c r="AG49" s="4">
         <v>0.51892668902731198</v>
       </c>
       <c r="AH49" s="1">
@@ -9255,1842 +9341,1842 @@
         <v>17.132000000000001</v>
       </c>
     </row>
-    <row r="50" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A50" s="5">
+    <row r="50" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A50" s="4">
         <v>42</v>
       </c>
-      <c r="B50" s="5" t="s">
+      <c r="B50" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C50" s="5" t="s">
+      <c r="C50" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D50" s="5" t="s">
+      <c r="D50" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E50" s="6" t="s">
+      <c r="E50" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F50" s="5">
+      <c r="F50" s="4">
         <v>0.01</v>
       </c>
-      <c r="G50" s="5">
+      <c r="G50" s="4">
         <v>16</v>
       </c>
-      <c r="H50" s="5">
+      <c r="H50" s="4">
         <v>8</v>
       </c>
-      <c r="I50" s="5">
+      <c r="I50" s="4">
         <v>2</v>
       </c>
-      <c r="J50" s="5">
-        <v>400</v>
-      </c>
-      <c r="K50" s="5">
-        <v>400</v>
-      </c>
-      <c r="L50" s="6" t="s">
+      <c r="J50" s="4">
+        <v>400</v>
+      </c>
+      <c r="K50" s="4">
+        <v>400</v>
+      </c>
+      <c r="L50" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="M50" s="5" t="s">
+      <c r="M50" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="N50" s="5">
+      <c r="N50" s="4">
         <v>2000</v>
       </c>
-      <c r="O50" s="5" t="s">
+      <c r="O50" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P50" s="6" t="s">
+      <c r="P50" s="5" t="s">
         <v>515</v>
       </c>
-      <c r="Q50" s="7">
+      <c r="Q50" s="6">
         <v>0.46927207637231499</v>
       </c>
-      <c r="R50" s="6" t="s">
+      <c r="R50" s="5" t="s">
         <v>516</v>
       </c>
-      <c r="S50" s="6" t="s">
+      <c r="S50" s="5" t="s">
         <v>517</v>
       </c>
-      <c r="T50" s="5">
+      <c r="T50" s="4">
         <v>0.36806148590947901</v>
       </c>
-      <c r="U50" s="6" t="s">
+      <c r="U50" s="5" t="s">
         <v>475</v>
       </c>
-      <c r="V50" s="6" t="s">
+      <c r="V50" s="5" t="s">
         <v>518</v>
       </c>
-      <c r="W50" s="6" t="s">
+      <c r="W50" s="5" t="s">
         <v>519</v>
       </c>
-      <c r="X50" s="5">
+      <c r="X50" s="4">
         <v>0.61581920903954801</v>
       </c>
-      <c r="Y50" s="6" t="s">
+      <c r="Y50" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="Z50" s="6">
+      <c r="Z50" s="5">
         <v>0.51750477402927997</v>
       </c>
-      <c r="AA50" s="6">
+      <c r="AA50" s="5">
         <v>0.40157480314960597</v>
       </c>
-      <c r="AB50" s="6">
+      <c r="AB50" s="5">
         <v>0.44478844169246601</v>
       </c>
-      <c r="AC50" s="6">
+      <c r="AC50" s="5">
         <v>0.39285714285714202</v>
       </c>
-      <c r="AD50" s="6">
+      <c r="AD50" s="5">
         <v>0.707317073170731</v>
       </c>
-      <c r="AE50" s="6">
+      <c r="AE50" s="5">
         <v>0.53787878787878696</v>
       </c>
-      <c r="AF50" s="6">
+      <c r="AF50" s="5">
         <v>0.64117647058823501</v>
       </c>
-      <c r="AG50" s="6">
+      <c r="AG50" s="5">
         <v>0.43889508928571402</v>
       </c>
-      <c r="AH50" s="6">
+      <c r="AH50" s="5">
         <v>0.55761316872427902</v>
       </c>
-      <c r="AI50" s="6">
+      <c r="AI50" s="5">
         <v>0.19172932330827</v>
       </c>
-      <c r="AJ50" s="6">
+      <c r="AJ50" s="5">
         <v>0.31391114348142701</v>
       </c>
-      <c r="AK50" s="6">
+      <c r="AK50" s="5">
         <v>0.35483870967741898</v>
       </c>
-      <c r="AL50" s="6">
+      <c r="AL50" s="5">
         <v>0.78378378378378299</v>
       </c>
-      <c r="AM50" s="6">
+      <c r="AM50" s="5">
         <v>0.440993788819875</v>
       </c>
-      <c r="AN50" s="5">
+      <c r="AN50" s="4">
         <v>0.59239130434782605</v>
       </c>
-      <c r="AO50" s="5">
+      <c r="AO50" s="4">
         <v>9.6757000000000009</v>
       </c>
-      <c r="AP50" s="5">
+      <c r="AP50" s="4">
         <v>187.68700000000001</v>
       </c>
-      <c r="AQ50" s="5">
+      <c r="AQ50" s="4">
         <v>11.782</v>
       </c>
     </row>
-    <row r="51" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A51" s="5">
+    <row r="51" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A51" s="4">
         <v>42</v>
       </c>
-      <c r="B51" s="5" t="s">
+      <c r="B51" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C51" s="5" t="s">
+      <c r="C51" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D51" s="5" t="s">
+      <c r="D51" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E51" s="6" t="s">
+      <c r="E51" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F51" s="5">
+      <c r="F51" s="4">
         <v>0.01</v>
       </c>
-      <c r="G51" s="5">
+      <c r="G51" s="4">
         <v>16</v>
       </c>
-      <c r="H51" s="5">
+      <c r="H51" s="4">
         <v>8</v>
       </c>
-      <c r="I51" s="5">
+      <c r="I51" s="4">
         <v>2</v>
       </c>
-      <c r="J51" s="5">
-        <v>400</v>
-      </c>
-      <c r="K51" s="5">
-        <v>400</v>
-      </c>
-      <c r="L51" s="6" t="s">
+      <c r="J51" s="4">
+        <v>400</v>
+      </c>
+      <c r="K51" s="4">
+        <v>400</v>
+      </c>
+      <c r="L51" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="M51" s="5" t="s">
+      <c r="M51" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N51" s="5">
+      <c r="N51" s="4">
         <v>2000</v>
       </c>
-      <c r="O51" s="5" t="s">
+      <c r="O51" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P51" s="6" t="s">
+      <c r="P51" s="5" t="s">
         <v>523</v>
       </c>
-      <c r="Q51" s="8">
+      <c r="Q51" s="7">
         <v>0.47374737473747303</v>
       </c>
-      <c r="R51" s="6" t="s">
+      <c r="R51" s="5" t="s">
         <v>524</v>
       </c>
-      <c r="S51" s="5">
+      <c r="S51" s="4">
         <v>0.28287841191066998</v>
       </c>
-      <c r="T51" s="5">
+      <c r="T51" s="4">
         <v>0.37732656514382401</v>
       </c>
-      <c r="U51" s="6" t="s">
+      <c r="U51" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="V51" s="6" t="s">
+      <c r="V51" s="5" t="s">
         <v>526</v>
       </c>
-      <c r="W51" s="6" t="s">
+      <c r="W51" s="5" t="s">
         <v>527</v>
       </c>
-      <c r="X51" s="6" t="s">
+      <c r="X51" s="5" t="s">
         <v>528</v>
       </c>
-      <c r="Y51" s="6" t="s">
+      <c r="Y51" s="5" t="s">
         <v>529</v>
       </c>
-      <c r="Z51" s="6">
+      <c r="Z51" s="5">
         <v>0.53360215053763405</v>
       </c>
-      <c r="AA51" s="6">
+      <c r="AA51" s="5">
         <v>0.41605839416058299</v>
       </c>
-      <c r="AB51" s="5">
+      <c r="AB51" s="4">
         <v>0.45005045408678102</v>
       </c>
-      <c r="AC51" s="6">
+      <c r="AC51" s="5">
         <v>0.42307692307692302</v>
       </c>
-      <c r="AD51" s="6">
+      <c r="AD51" s="5">
         <v>0.70967741935483797</v>
       </c>
-      <c r="AE51" s="6">
+      <c r="AE51" s="5">
         <v>0.54014598540145897</v>
       </c>
-      <c r="AF51" s="6">
+      <c r="AF51" s="5">
         <v>0.60893854748603304</v>
       </c>
-      <c r="AG51" s="6">
+      <c r="AG51" s="5">
         <v>0.44056919642857101</v>
       </c>
-      <c r="AH51" s="6">
+      <c r="AH51" s="5">
         <v>0.54458161865569199</v>
       </c>
-      <c r="AI51" s="6">
+      <c r="AI51" s="5">
         <v>0.214285714285714</v>
       </c>
-      <c r="AJ51" s="6">
+      <c r="AJ51" s="5">
         <v>0.324836125273124</v>
       </c>
-      <c r="AK51" s="6">
+      <c r="AK51" s="5">
         <v>0.35483870967741898</v>
       </c>
-      <c r="AL51" s="6">
+      <c r="AL51" s="5">
         <v>0.79279279279279202</v>
       </c>
-      <c r="AM51" s="6">
+      <c r="AM51" s="5">
         <v>0.45962732919254601</v>
       </c>
-      <c r="AN51" s="5">
+      <c r="AN51" s="4">
         <v>0.59239130434782605</v>
       </c>
-      <c r="AO51" s="5">
+      <c r="AO51" s="4">
         <v>9.3495000000000008</v>
       </c>
-      <c r="AP51" s="5">
+      <c r="AP51" s="4">
         <v>194.23400000000001</v>
       </c>
-      <c r="AQ51" s="5">
+      <c r="AQ51" s="4">
         <v>12.193</v>
       </c>
     </row>
-    <row r="52" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A52" s="5">
+    <row r="52" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A52" s="4">
         <v>42</v>
       </c>
-      <c r="B52" s="5" t="s">
+      <c r="B52" s="4" t="s">
         <v>511</v>
       </c>
-      <c r="C52" s="5" t="s">
+      <c r="C52" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D52" s="5" t="s">
+      <c r="D52" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E52" s="6" t="s">
+      <c r="E52" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F52" s="5">
+      <c r="F52" s="4">
         <v>0.01</v>
       </c>
-      <c r="G52" s="5">
+      <c r="G52" s="4">
         <v>16</v>
       </c>
-      <c r="H52" s="5">
+      <c r="H52" s="4">
         <v>8</v>
       </c>
-      <c r="I52" s="5">
+      <c r="I52" s="4">
         <v>2</v>
       </c>
-      <c r="J52" s="5">
-        <v>400</v>
-      </c>
-      <c r="K52" s="5">
-        <v>400</v>
-      </c>
-      <c r="L52" s="6" t="s">
+      <c r="J52" s="4">
+        <v>400</v>
+      </c>
+      <c r="K52" s="4">
+        <v>400</v>
+      </c>
+      <c r="L52" s="5" t="s">
         <v>514</v>
       </c>
-      <c r="M52" s="5" t="s">
+      <c r="M52" s="4" t="s">
         <v>628</v>
       </c>
-      <c r="N52" s="5">
+      <c r="N52" s="4">
         <v>2000</v>
       </c>
-      <c r="O52" s="5" t="s">
+      <c r="O52" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P52" s="6" t="s">
+      <c r="P52" s="5" t="s">
         <v>539</v>
       </c>
-      <c r="Q52" s="8">
+      <c r="Q52" s="7">
         <v>0.519433251007409</v>
       </c>
-      <c r="R52" s="6" t="s">
+      <c r="R52" s="5" t="s">
         <v>540</v>
       </c>
-      <c r="S52" s="6" t="s">
+      <c r="S52" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="T52" s="6" t="s">
+      <c r="T52" s="5" t="s">
         <v>542</v>
       </c>
-      <c r="U52" s="6" t="s">
+      <c r="U52" s="5" t="s">
         <v>543</v>
       </c>
-      <c r="V52" s="6" t="s">
+      <c r="V52" s="5" t="s">
         <v>544</v>
       </c>
-      <c r="W52" s="6" t="s">
+      <c r="W52" s="5" t="s">
         <v>545</v>
       </c>
-      <c r="X52" s="5">
+      <c r="X52" s="4">
         <v>0.71396895787139703</v>
       </c>
-      <c r="Y52" s="6" t="s">
+      <c r="Y52" s="5" t="s">
         <v>546</v>
       </c>
-      <c r="Z52" s="6">
+      <c r="Z52" s="5">
         <v>0.586080586080586</v>
       </c>
-      <c r="AA52" s="6">
+      <c r="AA52" s="5">
         <v>0.43181818181818099</v>
       </c>
-      <c r="AB52" s="6">
+      <c r="AB52" s="5">
         <v>0.49003984063744999</v>
       </c>
-      <c r="AC52" s="6">
+      <c r="AC52" s="5">
         <v>0.62903225806451601</v>
       </c>
-      <c r="AD52" s="6">
+      <c r="AD52" s="5">
         <v>0.73809523809523803</v>
       </c>
-      <c r="AE52" s="6">
+      <c r="AE52" s="5">
         <v>0.69101123595505598</v>
       </c>
-      <c r="AF52" s="6">
+      <c r="AF52" s="5">
         <v>0.75233644859812998</v>
       </c>
-      <c r="AG52" s="6">
+      <c r="AG52" s="5">
         <v>0.478677527551509</v>
       </c>
-      <c r="AH52" s="6">
+      <c r="AH52" s="5">
         <v>0.58287795992713998</v>
       </c>
-      <c r="AI52" s="5">
+      <c r="AI52" s="4">
         <v>0.19</v>
       </c>
-      <c r="AJ52" s="6">
+      <c r="AJ52" s="5">
         <v>0.36716417910447702</v>
       </c>
-      <c r="AK52" s="6">
+      <c r="AK52" s="5">
         <v>0.506493506493506</v>
       </c>
-      <c r="AL52" s="6">
+      <c r="AL52" s="5">
         <v>0.62626262626262597</v>
       </c>
-      <c r="AM52" s="6">
+      <c r="AM52" s="5">
         <v>0.51464435146443499</v>
       </c>
-      <c r="AN52" s="5">
+      <c r="AN52" s="4">
         <v>0.67932489451476796</v>
       </c>
-      <c r="AO52" s="5">
+      <c r="AO52" s="4">
         <v>8.3201999999999998</v>
       </c>
-      <c r="AP52" s="5">
+      <c r="AP52" s="4">
         <v>182.68700000000001</v>
       </c>
-      <c r="AQ52" s="5">
+      <c r="AQ52" s="4">
         <v>11.417999999999999</v>
       </c>
     </row>
-    <row r="53" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A53" s="5">
+    <row r="53" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A53" s="4">
         <v>42</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="4" t="s">
         <v>521</v>
       </c>
-      <c r="C53" s="5" t="s">
+      <c r="C53" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D53" s="5" t="s">
+      <c r="D53" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E53" s="6" t="s">
+      <c r="E53" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F53" s="5">
+      <c r="F53" s="4">
         <v>0.01</v>
       </c>
-      <c r="G53" s="5">
+      <c r="G53" s="4">
         <v>16</v>
       </c>
-      <c r="H53" s="5">
+      <c r="H53" s="4">
         <v>8</v>
       </c>
-      <c r="I53" s="5">
+      <c r="I53" s="4">
         <v>2</v>
       </c>
-      <c r="J53" s="5">
-        <v>400</v>
-      </c>
-      <c r="K53" s="5">
-        <v>400</v>
-      </c>
-      <c r="L53" s="6" t="s">
+      <c r="J53" s="4">
+        <v>400</v>
+      </c>
+      <c r="K53" s="4">
+        <v>400</v>
+      </c>
+      <c r="L53" s="5" t="s">
         <v>522</v>
       </c>
-      <c r="M53" s="5" t="s">
+      <c r="M53" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N53" s="5">
+      <c r="N53" s="4">
         <v>2000</v>
       </c>
-      <c r="O53" s="5" t="s">
+      <c r="O53" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P53" s="6" t="s">
+      <c r="P53" s="5" t="s">
         <v>547</v>
       </c>
-      <c r="Q53" s="8">
+      <c r="Q53" s="7">
         <v>0.51430070847546505</v>
       </c>
-      <c r="R53" s="6" t="s">
+      <c r="R53" s="5" t="s">
         <v>548</v>
       </c>
-      <c r="S53" s="6" t="s">
+      <c r="S53" s="5" t="s">
         <v>549</v>
       </c>
-      <c r="T53" s="6" t="s">
+      <c r="T53" s="5" t="s">
         <v>550</v>
       </c>
-      <c r="U53" s="6" t="s">
+      <c r="U53" s="5" t="s">
         <v>551</v>
       </c>
-      <c r="V53" s="6" t="s">
+      <c r="V53" s="5" t="s">
         <v>552</v>
       </c>
-      <c r="W53" s="6" t="s">
+      <c r="W53" s="5" t="s">
         <v>553</v>
       </c>
-      <c r="X53" s="6" t="s">
+      <c r="X53" s="5" t="s">
         <v>554</v>
       </c>
-      <c r="Y53" s="5">
+      <c r="Y53" s="4">
         <v>0.56844547563805103</v>
       </c>
-      <c r="Z53" s="6">
+      <c r="Z53" s="5">
         <v>0.58653846153846101</v>
       </c>
-      <c r="AA53" s="6">
+      <c r="AA53" s="5">
         <v>0.41379310344827502</v>
       </c>
-      <c r="AB53" s="6">
+      <c r="AB53" s="5">
         <v>0.49086576648133401</v>
       </c>
-      <c r="AC53" s="6">
+      <c r="AC53" s="5">
         <v>0.63793103448275801</v>
       </c>
-      <c r="AD53" s="6">
+      <c r="AD53" s="5">
         <v>0.74698795180722799</v>
       </c>
-      <c r="AE53" s="6">
+      <c r="AE53" s="5">
         <v>0.72928176795580102</v>
       </c>
-      <c r="AF53" s="6">
+      <c r="AF53" s="5">
         <v>0.72727272727272696</v>
       </c>
-      <c r="AG53" s="6">
+      <c r="AG53" s="5">
         <v>0.46957355055103001</v>
       </c>
-      <c r="AH53" s="6">
+      <c r="AH53" s="5">
         <v>0.55555555555555503</v>
       </c>
-      <c r="AI53" s="5">
+      <c r="AI53" s="4">
         <v>0.18</v>
       </c>
-      <c r="AJ53" s="5">
+      <c r="AJ53" s="4">
         <v>0.36895522388059698</v>
       </c>
-      <c r="AK53" s="6">
+      <c r="AK53" s="5">
         <v>0.48051948051948001</v>
       </c>
-      <c r="AL53" s="6">
+      <c r="AL53" s="5">
         <v>0.62626262626262597</v>
       </c>
-      <c r="AM53" s="6">
+      <c r="AM53" s="5">
         <v>0.55230125523012497</v>
       </c>
-      <c r="AN53" s="6">
+      <c r="AN53" s="5">
         <v>0.67510548523206704</v>
       </c>
-      <c r="AO53" s="5">
+      <c r="AO53" s="4">
         <v>8.0603999999999996</v>
       </c>
-      <c r="AP53" s="5">
+      <c r="AP53" s="4">
         <v>188.57599999999999</v>
       </c>
-      <c r="AQ53" s="5">
+      <c r="AQ53" s="4">
         <v>11.786</v>
       </c>
     </row>
-    <row r="54" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A54" s="5">
+    <row r="54" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A54" s="4">
         <v>42</v>
       </c>
-      <c r="B54" s="5" t="s">
+      <c r="B54" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C54" s="5" t="s">
+      <c r="C54" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D54" s="5" t="s">
+      <c r="D54" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E54" s="6" t="s">
+      <c r="E54" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F54" s="5">
+      <c r="F54" s="4">
         <v>0.01</v>
       </c>
-      <c r="G54" s="5">
+      <c r="G54" s="4">
         <v>16</v>
       </c>
-      <c r="H54" s="5">
+      <c r="H54" s="4">
         <v>8</v>
       </c>
-      <c r="I54" s="5">
+      <c r="I54" s="4">
         <v>2</v>
       </c>
-      <c r="J54" s="5">
-        <v>400</v>
-      </c>
-      <c r="K54" s="5">
-        <v>400</v>
-      </c>
-      <c r="L54" s="6" t="s">
+      <c r="J54" s="4">
+        <v>400</v>
+      </c>
+      <c r="K54" s="4">
+        <v>400</v>
+      </c>
+      <c r="L54" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="M54" s="5" t="s">
+      <c r="M54" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N54" s="5">
+      <c r="N54" s="4">
         <v>2000</v>
       </c>
-      <c r="O54" s="5" t="s">
+      <c r="O54" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P54" s="6" t="s">
+      <c r="P54" s="5" t="s">
         <v>566</v>
       </c>
-      <c r="Q54" s="8">
+      <c r="Q54" s="7">
         <v>0.50123492663082903</v>
       </c>
-      <c r="R54" s="5">
+      <c r="R54" s="4">
         <v>0.56413746172167401</v>
       </c>
-      <c r="S54" s="6" t="s">
+      <c r="S54" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="T54" s="6" t="s">
+      <c r="T54" s="5" t="s">
         <v>568</v>
       </c>
-      <c r="U54" s="6" t="s">
+      <c r="U54" s="5" t="s">
         <v>101</v>
       </c>
-      <c r="V54" s="6" t="s">
+      <c r="V54" s="5" t="s">
         <v>326</v>
       </c>
-      <c r="W54" s="6" t="s">
+      <c r="W54" s="5" t="s">
         <v>569</v>
       </c>
-      <c r="X54" s="6" t="s">
+      <c r="X54" s="5" t="s">
         <v>570</v>
       </c>
-      <c r="Y54" s="6" t="s">
+      <c r="Y54" s="5" t="s">
         <v>571</v>
       </c>
-      <c r="Z54" s="6">
+      <c r="Z54" s="5">
         <v>0.55975692099932395</v>
       </c>
-      <c r="AA54" s="6">
+      <c r="AA54" s="5">
         <v>0.439024390243902</v>
       </c>
-      <c r="AB54" s="6">
+      <c r="AB54" s="5">
         <v>0.45284621920135898</v>
       </c>
-      <c r="AC54" s="6">
+      <c r="AC54" s="5">
         <v>0.44444444444444398</v>
       </c>
-      <c r="AD54" s="6">
+      <c r="AD54" s="5">
         <v>0.723577235772357</v>
       </c>
-      <c r="AE54" s="6">
+      <c r="AE54" s="5">
         <v>0.56164383561643805</v>
       </c>
-      <c r="AF54" s="6">
+      <c r="AF54" s="5">
         <v>0.59668508287292799</v>
       </c>
-      <c r="AG54" s="6">
+      <c r="AG54" s="5">
         <v>0.48130580357142799</v>
       </c>
-      <c r="AH54" s="6">
+      <c r="AH54" s="5">
         <v>0.56858710562414205</v>
       </c>
-      <c r="AI54" s="6">
+      <c r="AI54" s="5">
         <v>0.27067669172932302</v>
       </c>
-      <c r="AJ54" s="6">
+      <c r="AJ54" s="5">
         <v>0.38820101966496701</v>
       </c>
-      <c r="AK54" s="6">
+      <c r="AK54" s="5">
         <v>0.38709677419354799</v>
       </c>
-      <c r="AL54" s="6">
+      <c r="AL54" s="5">
         <v>0.80180180180180105</v>
       </c>
-      <c r="AM54" s="6">
+      <c r="AM54" s="5">
         <v>0.50931677018633503</v>
       </c>
-      <c r="AN54" s="6">
+      <c r="AN54" s="5">
         <v>0.58695652173913004</v>
       </c>
-      <c r="AO54" s="5">
+      <c r="AO54" s="4">
         <v>9.1692</v>
       </c>
-      <c r="AP54" s="5">
+      <c r="AP54" s="4">
         <v>198.05500000000001</v>
       </c>
-      <c r="AQ54" s="5">
+      <c r="AQ54" s="4">
         <v>12.433</v>
       </c>
     </row>
-    <row r="55" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A55" s="5">
+    <row r="55" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A55" s="4">
         <v>42</v>
       </c>
-      <c r="B55" s="5" t="s">
+      <c r="B55" s="4" t="s">
         <v>564</v>
       </c>
-      <c r="C55" s="5" t="s">
+      <c r="C55" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D55" s="5" t="s">
+      <c r="D55" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E55" s="6" t="s">
+      <c r="E55" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F55" s="5">
+      <c r="F55" s="4">
         <v>0.01</v>
       </c>
-      <c r="G55" s="5">
+      <c r="G55" s="4">
         <v>16</v>
       </c>
-      <c r="H55" s="5">
+      <c r="H55" s="4">
         <v>8</v>
       </c>
-      <c r="I55" s="5">
+      <c r="I55" s="4">
         <v>2</v>
       </c>
-      <c r="J55" s="5">
-        <v>400</v>
-      </c>
-      <c r="K55" s="5">
-        <v>400</v>
-      </c>
-      <c r="L55" s="6" t="s">
+      <c r="J55" s="4">
+        <v>400</v>
+      </c>
+      <c r="K55" s="4">
+        <v>400</v>
+      </c>
+      <c r="L55" s="5" t="s">
         <v>565</v>
       </c>
-      <c r="M55" s="5" t="s">
+      <c r="M55" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N55" s="5">
+      <c r="N55" s="4">
         <v>2000</v>
       </c>
-      <c r="O55" s="5" t="s">
+      <c r="O55" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P55" s="6" t="s">
+      <c r="P55" s="5" t="s">
         <v>581</v>
       </c>
-      <c r="Q55" s="8">
+      <c r="Q55" s="7">
         <v>0.54267125908916902</v>
       </c>
-      <c r="R55" s="6" t="s">
+      <c r="R55" s="5" t="s">
         <v>582</v>
       </c>
-      <c r="S55" s="6" t="s">
+      <c r="S55" s="5" t="s">
         <v>583</v>
       </c>
-      <c r="T55" s="6" t="s">
+      <c r="T55" s="5" t="s">
         <v>584</v>
       </c>
-      <c r="U55" s="6" t="s">
+      <c r="U55" s="5" t="s">
         <v>585</v>
       </c>
-      <c r="V55" s="5">
+      <c r="V55" s="4">
         <v>0.72131147540983598</v>
       </c>
-      <c r="W55" s="6" t="s">
+      <c r="W55" s="5" t="s">
         <v>586</v>
       </c>
-      <c r="X55" s="6" t="s">
+      <c r="X55" s="5" t="s">
         <v>587</v>
       </c>
-      <c r="Y55" s="6" t="s">
+      <c r="Y55" s="5" t="s">
         <v>588</v>
       </c>
-      <c r="Z55" s="6">
+      <c r="Z55" s="5">
         <v>0.61454311454311406</v>
       </c>
-      <c r="AA55" s="6">
+      <c r="AA55" s="5">
         <v>0.54545454545454497</v>
       </c>
-      <c r="AB55" s="6">
+      <c r="AB55" s="5">
         <v>0.48450704225352098</v>
       </c>
-      <c r="AC55" s="6">
+      <c r="AC55" s="5">
         <v>0.57971014492753603</v>
       </c>
-      <c r="AD55" s="6">
+      <c r="AD55" s="5">
         <v>0.78571428571428503</v>
       </c>
-      <c r="AE55" s="6">
+      <c r="AE55" s="5">
         <v>0.73891625615763501</v>
       </c>
-      <c r="AF55" s="6">
+      <c r="AF55" s="5">
         <v>0.73728813559322004</v>
       </c>
-      <c r="AG55" s="6">
+      <c r="AG55" s="5">
         <v>0.50958313368471397</v>
       </c>
-      <c r="AH55" s="6">
+      <c r="AH55" s="5">
         <v>0.57984213721918598</v>
       </c>
-      <c r="AI55" s="5">
+      <c r="AI55" s="4">
         <v>0.27</v>
       </c>
-      <c r="AJ55" s="6">
+      <c r="AJ55" s="5">
         <v>0.41074626865671598</v>
       </c>
-      <c r="AK55" s="6">
+      <c r="AK55" s="5">
         <v>0.51948051948051899</v>
       </c>
-      <c r="AL55" s="6">
+      <c r="AL55" s="5">
         <v>0.66666666666666596</v>
       </c>
-      <c r="AM55" s="6">
+      <c r="AM55" s="5">
         <v>0.62761506276150603</v>
       </c>
-      <c r="AN55" s="6">
+      <c r="AN55" s="5">
         <v>0.734177215189873</v>
       </c>
-      <c r="AO55" s="5">
+      <c r="AO55" s="4">
         <v>8.2208000000000006</v>
       </c>
-      <c r="AP55" s="5">
+      <c r="AP55" s="4">
         <v>184.89699999999999</v>
       </c>
-      <c r="AQ55" s="5">
+      <c r="AQ55" s="4">
         <v>11.555999999999999</v>
       </c>
     </row>
-    <row r="56" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A56" s="5">
+    <row r="56" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A56" s="4">
         <v>42</v>
       </c>
-      <c r="B56" s="5" t="s">
+      <c r="B56" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="C56" s="5" t="s">
+      <c r="C56" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D56" s="5" t="s">
+      <c r="D56" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E56" s="6" t="s">
+      <c r="E56" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F56" s="5">
+      <c r="F56" s="4">
         <v>0.01</v>
       </c>
-      <c r="G56" s="5">
+      <c r="G56" s="4">
         <v>16</v>
       </c>
-      <c r="H56" s="5">
+      <c r="H56" s="4">
         <v>8</v>
       </c>
-      <c r="I56" s="5">
+      <c r="I56" s="4">
         <v>2</v>
       </c>
-      <c r="J56" s="5">
-        <v>400</v>
-      </c>
-      <c r="K56" s="5">
-        <v>400</v>
-      </c>
-      <c r="L56" s="6" t="s">
+      <c r="J56" s="4">
+        <v>400</v>
+      </c>
+      <c r="K56" s="4">
+        <v>400</v>
+      </c>
+      <c r="L56" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="M56" s="5" t="s">
+      <c r="M56" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N56" s="5">
+      <c r="N56" s="4">
         <v>2000</v>
       </c>
-      <c r="O56" s="5" t="s">
+      <c r="O56" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P56" s="6" t="s">
+      <c r="P56" s="5" t="s">
         <v>598</v>
       </c>
-      <c r="Q56" s="8">
+      <c r="Q56" s="7">
         <v>0.52613489904052602</v>
       </c>
-      <c r="R56" s="6" t="s">
+      <c r="R56" s="5" t="s">
         <v>599</v>
       </c>
-      <c r="S56" s="5">
+      <c r="S56" s="4">
         <v>0.36</v>
       </c>
-      <c r="T56" s="5">
+      <c r="T56" s="4">
         <v>0.45378151260504201</v>
       </c>
-      <c r="U56" s="6" t="s">
+      <c r="U56" s="5" t="s">
         <v>130</v>
       </c>
-      <c r="V56" s="6" t="s">
+      <c r="V56" s="5" t="s">
         <v>600</v>
       </c>
-      <c r="W56" s="6" t="s">
+      <c r="W56" s="5" t="s">
         <v>601</v>
       </c>
-      <c r="X56" s="6" t="s">
+      <c r="X56" s="5" t="s">
         <v>602</v>
       </c>
-      <c r="Y56" s="5">
+      <c r="Y56" s="4">
         <v>0.54045307443365698</v>
       </c>
-      <c r="Z56" s="6">
+      <c r="Z56" s="5">
         <v>0.57591973244147099</v>
       </c>
-      <c r="AA56" s="6">
+      <c r="AA56" s="5">
         <v>0.44021739130434701</v>
       </c>
-      <c r="AB56" s="6">
+      <c r="AB56" s="5">
         <v>0.477108433734939</v>
       </c>
-      <c r="AC56" s="6">
+      <c r="AC56" s="5">
         <v>0.46153846153846101</v>
       </c>
-      <c r="AD56" s="6">
+      <c r="AD56" s="5">
         <v>0.70634920634920595</v>
       </c>
-      <c r="AE56" s="6">
+      <c r="AE56" s="5">
         <v>0.59333333333333305</v>
       </c>
-      <c r="AF56" s="6">
+      <c r="AF56" s="5">
         <v>0.64161849710982599</v>
       </c>
-      <c r="AG56" s="6">
+      <c r="AG56" s="5">
         <v>0.51255580357142805</v>
       </c>
-      <c r="AH56" s="6">
+      <c r="AH56" s="5">
         <v>0.59053497942386801</v>
       </c>
-      <c r="AI56" s="6">
+      <c r="AI56" s="5">
         <v>0.30451127819548801</v>
       </c>
-      <c r="AJ56" s="6">
+      <c r="AJ56" s="5">
         <v>0.43262927895120101</v>
       </c>
-      <c r="AK56" s="6">
+      <c r="AK56" s="5">
         <v>0.38709677419354799</v>
       </c>
-      <c r="AL56" s="6">
+      <c r="AL56" s="5">
         <v>0.80180180180180105</v>
       </c>
-      <c r="AM56" s="6">
+      <c r="AM56" s="5">
         <v>0.5527950310559</v>
       </c>
-      <c r="AN56" s="6">
+      <c r="AN56" s="5">
         <v>0.60326086956521696</v>
       </c>
-      <c r="AO56" s="5">
+      <c r="AO56" s="4">
         <v>9.0181000000000004</v>
       </c>
-      <c r="AP56" s="5">
+      <c r="AP56" s="4">
         <v>201.37200000000001</v>
       </c>
-      <c r="AQ56" s="5">
+      <c r="AQ56" s="4">
         <v>12.641</v>
       </c>
     </row>
-    <row r="57" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A57" s="5">
+    <row r="57" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A57" s="4">
         <v>42</v>
       </c>
-      <c r="B57" s="5" t="s">
+      <c r="B57" s="4" t="s">
         <v>596</v>
       </c>
-      <c r="C57" s="5" t="s">
+      <c r="C57" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D57" s="5" t="s">
+      <c r="D57" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E57" s="6" t="s">
+      <c r="E57" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F57" s="5">
+      <c r="F57" s="4">
         <v>0.01</v>
       </c>
-      <c r="G57" s="5">
+      <c r="G57" s="4">
         <v>16</v>
       </c>
-      <c r="H57" s="5">
+      <c r="H57" s="4">
         <v>8</v>
       </c>
-      <c r="I57" s="5">
+      <c r="I57" s="4">
         <v>2</v>
       </c>
-      <c r="J57" s="5">
-        <v>400</v>
-      </c>
-      <c r="K57" s="5">
-        <v>400</v>
-      </c>
-      <c r="L57" s="6" t="s">
+      <c r="J57" s="4">
+        <v>400</v>
+      </c>
+      <c r="K57" s="4">
+        <v>400</v>
+      </c>
+      <c r="L57" s="5" t="s">
         <v>597</v>
       </c>
-      <c r="M57" s="5" t="s">
+      <c r="M57" s="4" t="s">
         <v>629</v>
       </c>
-      <c r="N57" s="5">
+      <c r="N57" s="4">
         <v>2000</v>
       </c>
-      <c r="O57" s="5" t="s">
+      <c r="O57" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P57" s="6" t="s">
+      <c r="P57" s="5" t="s">
         <v>610</v>
       </c>
-      <c r="Q57" s="8">
+      <c r="Q57" s="7">
         <v>0.55424409844299305</v>
       </c>
-      <c r="R57" s="6" t="s">
+      <c r="R57" s="5" t="s">
         <v>611</v>
       </c>
-      <c r="S57" s="6" t="s">
+      <c r="S57" s="5" t="s">
         <v>612</v>
       </c>
-      <c r="T57" s="6" t="s">
+      <c r="T57" s="5" t="s">
         <v>613</v>
       </c>
-      <c r="U57" s="6" t="s">
+      <c r="U57" s="5" t="s">
         <v>614</v>
       </c>
-      <c r="V57" s="6" t="s">
+      <c r="V57" s="5" t="s">
         <v>563</v>
       </c>
-      <c r="W57" s="6" t="s">
+      <c r="W57" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="X57" s="6" t="s">
+      <c r="X57" s="5" t="s">
         <v>616</v>
       </c>
-      <c r="Y57" s="6" t="s">
+      <c r="Y57" s="5" t="s">
         <v>617</v>
       </c>
-      <c r="Z57" s="6">
+      <c r="Z57" s="5">
         <v>0.61856325492689102</v>
       </c>
-      <c r="AA57" s="6">
+      <c r="AA57" s="5">
         <v>0.53703703703703698</v>
       </c>
-      <c r="AB57" s="6">
+      <c r="AB57" s="5">
         <v>0.488325550366911</v>
       </c>
-      <c r="AC57" s="6">
+      <c r="AC57" s="5">
         <v>0.63235294117647001</v>
       </c>
-      <c r="AD57" s="5">
+      <c r="AD57" s="4">
         <v>0.78823529411764703</v>
       </c>
-      <c r="AE57" s="6">
+      <c r="AE57" s="5">
         <v>0.73488372093023202</v>
       </c>
-      <c r="AF57" s="6">
+      <c r="AF57" s="5">
         <v>0.72727272727272696</v>
       </c>
-      <c r="AG57" s="6">
+      <c r="AG57" s="5">
         <v>0.52874940105414403</v>
       </c>
-      <c r="AH57" s="6">
+      <c r="AH57" s="5">
         <v>0.59077109896781999</v>
       </c>
-      <c r="AI57" s="5">
+      <c r="AI57" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ57" s="6">
+      <c r="AJ57" s="5">
         <v>0.43701492537313402</v>
       </c>
-      <c r="AK57" s="6">
+      <c r="AK57" s="5">
         <v>0.55844155844155796</v>
       </c>
-      <c r="AL57" s="6">
+      <c r="AL57" s="5">
         <v>0.67676767676767602</v>
       </c>
-      <c r="AM57" s="6">
+      <c r="AM57" s="5">
         <v>0.661087866108786</v>
       </c>
-      <c r="AN57" s="6">
+      <c r="AN57" s="5">
         <v>0.74261603375527396</v>
       </c>
-      <c r="AO57" s="5">
+      <c r="AO57" s="4">
         <v>8.0995000000000008</v>
       </c>
-      <c r="AP57" s="5">
+      <c r="AP57" s="4">
         <v>187.667</v>
       </c>
-      <c r="AQ57" s="5">
+      <c r="AQ57" s="4">
         <v>11.728999999999999</v>
       </c>
     </row>
-    <row r="58" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A58" s="5">
+    <row r="58" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A58" s="4">
         <v>43</v>
       </c>
-      <c r="B58" s="5" t="s">
+      <c r="B58" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C58" s="5" t="s">
+      <c r="C58" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D58" s="5" t="s">
+      <c r="D58" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E58" s="6" t="s">
+      <c r="E58" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F58" s="5">
+      <c r="F58" s="4">
         <v>0.01</v>
       </c>
-      <c r="G58" s="5">
+      <c r="G58" s="4">
         <v>16</v>
       </c>
-      <c r="H58" s="5">
+      <c r="H58" s="4">
         <v>8</v>
       </c>
-      <c r="I58" s="5">
+      <c r="I58" s="4">
         <v>2</v>
       </c>
-      <c r="J58" s="5">
-        <v>400</v>
-      </c>
-      <c r="K58" s="5">
-        <v>400</v>
-      </c>
-      <c r="L58" s="6" t="s">
+      <c r="J58" s="4">
+        <v>400</v>
+      </c>
+      <c r="K58" s="4">
+        <v>400</v>
+      </c>
+      <c r="L58" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="M58" s="5" t="s">
+      <c r="M58" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N58" s="5">
+      <c r="N58" s="4">
         <v>2000</v>
       </c>
-      <c r="O58" s="5" t="s">
+      <c r="O58" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P58" s="5">
+      <c r="P58" s="4">
         <v>0.60340577363967896</v>
       </c>
-      <c r="Q58" s="8">
+      <c r="Q58" s="7">
         <v>0.47472789622782102</v>
       </c>
-      <c r="R58" s="6" t="s">
+      <c r="R58" s="5" t="s">
         <v>532</v>
       </c>
-      <c r="S58" s="6" t="s">
+      <c r="S58" s="5" t="s">
         <v>533</v>
       </c>
-      <c r="T58" s="6" t="s">
+      <c r="T58" s="5" t="s">
         <v>534</v>
       </c>
-      <c r="U58" s="6" t="s">
+      <c r="U58" s="5" t="s">
         <v>480</v>
       </c>
-      <c r="V58" s="6" t="s">
+      <c r="V58" s="5" t="s">
         <v>535</v>
       </c>
-      <c r="W58" s="6" t="s">
+      <c r="W58" s="5" t="s">
         <v>536</v>
       </c>
-      <c r="X58" s="6" t="s">
+      <c r="X58" s="5" t="s">
         <v>537</v>
       </c>
-      <c r="Y58" s="6" t="s">
+      <c r="Y58" s="5" t="s">
         <v>538</v>
       </c>
-      <c r="Z58" s="6">
+      <c r="Z58" s="5">
         <v>0.52708058124174295</v>
       </c>
-      <c r="AA58" s="6">
+      <c r="AA58" s="5">
         <v>0.50862068965517204</v>
       </c>
-      <c r="AB58" s="5">
+      <c r="AB58" s="4">
         <v>0.4453125</v>
       </c>
-      <c r="AC58" s="5">
+      <c r="AC58" s="4">
         <v>0.44</v>
       </c>
-      <c r="AD58" s="6">
+      <c r="AD58" s="5">
         <v>0.68461538461538396</v>
       </c>
-      <c r="AE58" s="6">
+      <c r="AE58" s="5">
         <v>0.52238805970149205</v>
       </c>
-      <c r="AF58" s="6">
+      <c r="AF58" s="5">
         <v>0.60555555555555496</v>
       </c>
-      <c r="AG58" s="6">
+      <c r="AG58" s="5">
         <v>0.44419642857142799</v>
       </c>
-      <c r="AH58" s="6">
+      <c r="AH58" s="5">
         <v>0.54732510288065805</v>
       </c>
-      <c r="AI58" s="6">
+      <c r="AI58" s="5">
         <v>0.221804511278195</v>
       </c>
-      <c r="AJ58" s="6">
+      <c r="AJ58" s="5">
         <v>0.33211944646758901</v>
       </c>
-      <c r="AK58" s="6">
+      <c r="AK58" s="5">
         <v>0.35483870967741898</v>
       </c>
-      <c r="AL58" s="6">
+      <c r="AL58" s="5">
         <v>0.80180180180180105</v>
       </c>
-      <c r="AM58" s="6">
+      <c r="AM58" s="5">
         <v>0.434782608695652</v>
       </c>
-      <c r="AN58" s="5">
+      <c r="AN58" s="4">
         <v>0.59239130434782605</v>
       </c>
-      <c r="AO58" s="5">
+      <c r="AO58" s="4">
         <v>9.1350999999999996</v>
       </c>
-      <c r="AP58" s="5">
+      <c r="AP58" s="4">
         <v>198.79400000000001</v>
       </c>
-      <c r="AQ58" s="5">
+      <c r="AQ58" s="4">
         <v>12.478999999999999</v>
       </c>
     </row>
-    <row r="59" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A59" s="5">
+    <row r="59" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A59" s="4">
         <v>43</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="4" t="s">
         <v>530</v>
       </c>
-      <c r="C59" s="5" t="s">
+      <c r="C59" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D59" s="5" t="s">
+      <c r="D59" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E59" s="6" t="s">
+      <c r="E59" s="5" t="s">
         <v>45</v>
       </c>
-      <c r="F59" s="5">
+      <c r="F59" s="4">
         <v>0.01</v>
       </c>
-      <c r="G59" s="5">
+      <c r="G59" s="4">
         <v>16</v>
       </c>
-      <c r="H59" s="5">
+      <c r="H59" s="4">
         <v>8</v>
       </c>
-      <c r="I59" s="5">
+      <c r="I59" s="4">
         <v>2</v>
       </c>
-      <c r="J59" s="5">
-        <v>400</v>
-      </c>
-      <c r="K59" s="5">
-        <v>400</v>
-      </c>
-      <c r="L59" s="6" t="s">
+      <c r="J59" s="4">
+        <v>400</v>
+      </c>
+      <c r="K59" s="4">
+        <v>400</v>
+      </c>
+      <c r="L59" s="5" t="s">
         <v>531</v>
       </c>
-      <c r="M59" s="5" t="s">
+      <c r="M59" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N59" s="5">
+      <c r="N59" s="4">
         <v>2000</v>
       </c>
-      <c r="O59" s="5" t="s">
+      <c r="O59" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P59" s="6" t="s">
+      <c r="P59" s="5" t="s">
         <v>555</v>
       </c>
-      <c r="Q59" s="8">
+      <c r="Q59" s="7">
         <v>0.52371026576341795</v>
       </c>
-      <c r="R59" s="6" t="s">
+      <c r="R59" s="5" t="s">
         <v>556</v>
       </c>
-      <c r="S59" s="6" t="s">
+      <c r="S59" s="5" t="s">
         <v>557</v>
       </c>
-      <c r="T59" s="6" t="s">
+      <c r="T59" s="5" t="s">
         <v>558</v>
       </c>
-      <c r="U59" s="6" t="s">
+      <c r="U59" s="5" t="s">
         <v>559</v>
       </c>
-      <c r="V59" s="6" t="s">
+      <c r="V59" s="5" t="s">
         <v>455</v>
       </c>
-      <c r="W59" s="6" t="s">
+      <c r="W59" s="5" t="s">
         <v>560</v>
       </c>
-      <c r="X59" s="6" t="s">
+      <c r="X59" s="5" t="s">
         <v>561</v>
       </c>
-      <c r="Y59" s="6" t="s">
+      <c r="Y59" s="5" t="s">
         <v>562</v>
       </c>
-      <c r="Z59" s="6">
+      <c r="Z59" s="5">
         <v>0.60063492063491997</v>
       </c>
-      <c r="AA59" s="6">
+      <c r="AA59" s="5">
         <v>0.55263157894736803</v>
       </c>
-      <c r="AB59" s="6">
+      <c r="AB59" s="5">
         <v>0.48133748055987502</v>
       </c>
-      <c r="AC59" s="6">
+      <c r="AC59" s="5">
         <v>0.63076923076922997</v>
       </c>
-      <c r="AD59" s="6">
+      <c r="AD59" s="5">
         <v>0.74712643678160895</v>
       </c>
-      <c r="AE59" s="6">
+      <c r="AE59" s="5">
         <v>0.72826086956521696</v>
       </c>
-      <c r="AF59" s="6">
+      <c r="AF59" s="5">
         <v>0.71179039301309999</v>
       </c>
-      <c r="AG59" s="6">
+      <c r="AG59" s="5">
         <v>0.481552467656923</v>
       </c>
-      <c r="AH59" s="6">
+      <c r="AH59" s="5">
         <v>0.57437765634486904</v>
       </c>
-      <c r="AI59" s="5">
+      <c r="AI59" s="4">
         <v>0.21</v>
       </c>
-      <c r="AJ59" s="6">
+      <c r="AJ59" s="5">
         <v>0.36955223880596999</v>
       </c>
-      <c r="AK59" s="6">
+      <c r="AK59" s="5">
         <v>0.53246753246753198</v>
       </c>
-      <c r="AL59" s="6">
+      <c r="AL59" s="5">
         <v>0.65656565656565602</v>
       </c>
-      <c r="AM59" s="6">
+      <c r="AM59" s="5">
         <v>0.56066945606694496</v>
       </c>
-      <c r="AN59" s="6">
+      <c r="AN59" s="5">
         <v>0.68776371308016804</v>
       </c>
-      <c r="AO59" s="5">
+      <c r="AO59" s="4">
         <v>8.3061000000000007</v>
       </c>
-      <c r="AP59" s="5">
+      <c r="AP59" s="4">
         <v>182.99700000000001</v>
       </c>
-      <c r="AQ59" s="5">
+      <c r="AQ59" s="4">
         <v>11.436999999999999</v>
       </c>
     </row>
-    <row r="60" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A60" s="5">
+    <row r="60" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A60" s="4">
         <v>43</v>
       </c>
-      <c r="B60" s="5" t="s">
+      <c r="B60" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C60" s="5" t="s">
+      <c r="C60" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D60" s="5" t="s">
+      <c r="D60" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E60" s="6" t="s">
+      <c r="E60" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F60" s="5">
+      <c r="F60" s="4">
         <v>0.01</v>
       </c>
-      <c r="G60" s="5">
+      <c r="G60" s="4">
         <v>16</v>
       </c>
-      <c r="H60" s="5">
+      <c r="H60" s="4">
         <v>8</v>
       </c>
-      <c r="I60" s="5">
+      <c r="I60" s="4">
         <v>2</v>
       </c>
-      <c r="J60" s="5">
-        <v>400</v>
-      </c>
-      <c r="K60" s="5">
-        <v>400</v>
-      </c>
-      <c r="L60" s="5">
+      <c r="J60" s="4">
+        <v>400</v>
+      </c>
+      <c r="K60" s="4">
+        <v>400</v>
+      </c>
+      <c r="L60" s="4">
         <v>0.54904442475635995</v>
       </c>
-      <c r="M60" s="5" t="s">
+      <c r="M60" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N60" s="5">
+      <c r="N60" s="4">
         <v>2000</v>
       </c>
-      <c r="O60" s="5" t="s">
+      <c r="O60" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P60" s="6" t="s">
+      <c r="P60" s="5" t="s">
         <v>573</v>
       </c>
-      <c r="Q60" s="8">
+      <c r="Q60" s="7">
         <v>0.50945558739255004</v>
       </c>
-      <c r="R60" s="6" t="s">
+      <c r="R60" s="5" t="s">
         <v>574</v>
       </c>
-      <c r="S60" s="6" t="s">
+      <c r="S60" s="5" t="s">
         <v>575</v>
       </c>
-      <c r="T60" s="6" t="s">
+      <c r="T60" s="5" t="s">
         <v>576</v>
       </c>
-      <c r="U60" s="6" t="s">
+      <c r="U60" s="5" t="s">
         <v>90</v>
       </c>
-      <c r="V60" s="6" t="s">
+      <c r="V60" s="5" t="s">
         <v>577</v>
       </c>
-      <c r="W60" s="6" t="s">
+      <c r="W60" s="5" t="s">
         <v>578</v>
       </c>
-      <c r="X60" s="6" t="s">
+      <c r="X60" s="5" t="s">
         <v>579</v>
       </c>
-      <c r="Y60" s="6" t="s">
+      <c r="Y60" s="5" t="s">
         <v>580</v>
       </c>
-      <c r="Z60" s="6">
+      <c r="Z60" s="5">
         <v>0.56278763971071599</v>
       </c>
-      <c r="AA60" s="6">
+      <c r="AA60" s="5">
         <v>0.48051948051948001</v>
       </c>
-      <c r="AB60" s="6">
+      <c r="AB60" s="5">
         <v>0.44715447154471499</v>
       </c>
-      <c r="AC60" s="5">
+      <c r="AC60" s="4">
         <v>0.4375</v>
       </c>
-      <c r="AD60" s="6">
+      <c r="AD60" s="5">
         <v>0.66666666666666596</v>
       </c>
-      <c r="AE60" s="6">
+      <c r="AE60" s="5">
         <v>0.592592592592592</v>
       </c>
-      <c r="AF60" s="6">
+      <c r="AF60" s="5">
         <v>0.60416666666666596</v>
       </c>
-      <c r="AG60" s="5">
+      <c r="AG60" s="4">
         <v>0.49609375</v>
       </c>
-      <c r="AH60" s="6">
+      <c r="AH60" s="5">
         <v>0.58710562414266099</v>
       </c>
-      <c r="AI60" s="6">
+      <c r="AI60" s="5">
         <v>0.278195488721804</v>
       </c>
-      <c r="AJ60" s="6">
+      <c r="AJ60" s="5">
         <v>0.40058266569555701</v>
       </c>
-      <c r="AK60" s="6">
+      <c r="AK60" s="5">
         <v>0.45161290322580599</v>
       </c>
-      <c r="AL60" s="6">
+      <c r="AL60" s="5">
         <v>0.79279279279279202</v>
       </c>
-      <c r="AM60" s="6">
+      <c r="AM60" s="5">
         <v>0.49689440993788803</v>
       </c>
-      <c r="AN60" s="6">
+      <c r="AN60" s="5">
         <v>0.63043478260869501</v>
       </c>
-      <c r="AO60" s="5">
+      <c r="AO60" s="4">
         <v>9.0897000000000006</v>
       </c>
-      <c r="AP60" s="5">
+      <c r="AP60" s="4">
         <v>199.786</v>
       </c>
-      <c r="AQ60" s="5">
+      <c r="AQ60" s="4">
         <v>12.542</v>
       </c>
     </row>
-    <row r="61" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A61" s="5">
+    <row r="61" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A61" s="4">
         <v>43</v>
       </c>
-      <c r="B61" s="5" t="s">
+      <c r="B61" s="4" t="s">
         <v>572</v>
       </c>
-      <c r="C61" s="5" t="s">
+      <c r="C61" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D61" s="5" t="s">
+      <c r="D61" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E61" s="6" t="s">
+      <c r="E61" s="5" t="s">
         <v>84</v>
       </c>
-      <c r="F61" s="5">
+      <c r="F61" s="4">
         <v>0.01</v>
       </c>
-      <c r="G61" s="5">
+      <c r="G61" s="4">
         <v>16</v>
       </c>
-      <c r="H61" s="5">
+      <c r="H61" s="4">
         <v>8</v>
       </c>
-      <c r="I61" s="5">
+      <c r="I61" s="4">
         <v>2</v>
       </c>
-      <c r="J61" s="5">
-        <v>400</v>
-      </c>
-      <c r="K61" s="5">
-        <v>400</v>
-      </c>
-      <c r="L61" s="5">
+      <c r="J61" s="4">
+        <v>400</v>
+      </c>
+      <c r="K61" s="4">
+        <v>400</v>
+      </c>
+      <c r="L61" s="4">
         <v>0.54904442475635995</v>
       </c>
-      <c r="M61" s="5" t="s">
+      <c r="M61" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N61" s="5">
+      <c r="N61" s="4">
         <v>2000</v>
       </c>
-      <c r="O61" s="5" t="s">
+      <c r="O61" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P61" s="6" t="s">
+      <c r="P61" s="5" t="s">
         <v>589</v>
       </c>
-      <c r="Q61" s="7">
+      <c r="Q61" s="6">
         <v>0.54904442475635995</v>
       </c>
-      <c r="R61" s="6" t="s">
+      <c r="R61" s="5" t="s">
         <v>590</v>
       </c>
-      <c r="S61" s="6" t="s">
+      <c r="S61" s="5" t="s">
         <v>591</v>
       </c>
-      <c r="T61" s="6" t="s">
+      <c r="T61" s="5" t="s">
         <v>592</v>
       </c>
-      <c r="U61" s="6" t="s">
+      <c r="U61" s="5" t="s">
         <v>593</v>
       </c>
-      <c r="V61" s="6" t="s">
+      <c r="V61" s="5" t="s">
         <v>594</v>
       </c>
-      <c r="W61" s="5">
+      <c r="W61" s="4">
         <v>0.67268623024830698</v>
       </c>
-      <c r="X61" s="6" t="s">
+      <c r="X61" s="5" t="s">
         <v>595</v>
       </c>
-      <c r="Y61" s="5">
+      <c r="Y61" s="4">
         <v>0.58196941239602895</v>
       </c>
-      <c r="Z61" s="6">
+      <c r="Z61" s="5">
         <v>0.61804222648752305</v>
       </c>
-      <c r="AA61" s="6">
+      <c r="AA61" s="5">
         <v>0.54716981132075404</v>
       </c>
-      <c r="AB61" s="6">
+      <c r="AB61" s="5">
         <v>0.48624484181568001</v>
       </c>
-      <c r="AC61" s="6">
+      <c r="AC61" s="5">
         <v>0.602739726027397</v>
       </c>
-      <c r="AD61" s="6">
+      <c r="AD61" s="5">
         <v>0.81927710843373402</v>
       </c>
-      <c r="AE61" s="6">
+      <c r="AE61" s="5">
         <v>0.73039215686274495</v>
       </c>
-      <c r="AF61" s="6">
+      <c r="AF61" s="5">
         <v>0.72540983606557297</v>
       </c>
-      <c r="AG61" s="6">
+      <c r="AG61" s="5">
         <v>0.51964542405366498</v>
       </c>
-      <c r="AH61" s="6">
+      <c r="AH61" s="5">
         <v>0.58652094717668402</v>
       </c>
-      <c r="AI61" s="5">
+      <c r="AI61" s="4">
         <v>0.28999999999999998</v>
       </c>
-      <c r="AJ61" s="6">
+      <c r="AJ61" s="5">
         <v>0.42208955223880501</v>
       </c>
-      <c r="AK61" s="6">
+      <c r="AK61" s="5">
         <v>0.57142857142857095</v>
       </c>
-      <c r="AL61" s="6">
+      <c r="AL61" s="5">
         <v>0.68686868686868596</v>
       </c>
-      <c r="AM61" s="6">
+      <c r="AM61" s="5">
         <v>0.62343096234309603</v>
       </c>
-      <c r="AN61" s="6">
+      <c r="AN61" s="5">
         <v>0.746835443037974</v>
       </c>
-      <c r="AO61" s="5">
+      <c r="AO61" s="4">
         <v>7.8064999999999998</v>
       </c>
-      <c r="AP61" s="5">
+      <c r="AP61" s="4">
         <v>194.71</v>
       </c>
-      <c r="AQ61" s="5">
+      <c r="AQ61" s="4">
         <v>12.169</v>
       </c>
     </row>
-    <row r="62" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A62" s="5">
+    <row r="62" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A62" s="4">
         <v>43</v>
       </c>
-      <c r="B62" s="5" t="s">
+      <c r="B62" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="C62" s="5" t="s">
+      <c r="C62" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D62" s="5" t="s">
+      <c r="D62" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E62" s="6" t="s">
+      <c r="E62" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F62" s="5">
+      <c r="F62" s="4">
         <v>0.01</v>
       </c>
-      <c r="G62" s="5">
+      <c r="G62" s="4">
         <v>16</v>
       </c>
-      <c r="H62" s="5">
+      <c r="H62" s="4">
         <v>8</v>
       </c>
-      <c r="I62" s="5">
+      <c r="I62" s="4">
         <v>2</v>
       </c>
-      <c r="J62" s="5">
-        <v>400</v>
-      </c>
-      <c r="K62" s="5">
-        <v>400</v>
-      </c>
-      <c r="L62" s="6" t="s">
+      <c r="J62" s="4">
+        <v>400</v>
+      </c>
+      <c r="K62" s="4">
+        <v>400</v>
+      </c>
+      <c r="L62" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M62" s="5" t="s">
+      <c r="M62" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N62" s="5">
+      <c r="N62" s="4">
         <v>2000</v>
       </c>
-      <c r="O62" s="5" t="s">
+      <c r="O62" s="4" t="s">
         <v>46</v>
       </c>
-      <c r="P62" s="6" t="s">
+      <c r="P62" s="5" t="s">
         <v>605</v>
       </c>
-      <c r="Q62" s="7">
+      <c r="Q62" s="6">
         <v>0.51576094708315501</v>
       </c>
-      <c r="R62" s="6" t="s">
+      <c r="R62" s="5" t="s">
         <v>606</v>
       </c>
-      <c r="S62" s="5">
+      <c r="S62" s="4">
         <v>0.375</v>
       </c>
-      <c r="T62" s="6" t="s">
+      <c r="T62" s="5" t="s">
         <v>607</v>
       </c>
-      <c r="U62" s="6" t="s">
+      <c r="U62" s="5" t="s">
         <v>525</v>
       </c>
-      <c r="V62" s="6" t="s">
+      <c r="V62" s="5" t="s">
         <v>468</v>
       </c>
-      <c r="W62" s="6" t="s">
+      <c r="W62" s="5" t="s">
         <v>608</v>
       </c>
-      <c r="X62" s="6" t="s">
+      <c r="X62" s="5" t="s">
         <v>609</v>
       </c>
-      <c r="Y62" s="5">
+      <c r="Y62" s="4">
         <v>0.52757513860519401</v>
       </c>
-      <c r="Z62" s="5">
+      <c r="Z62" s="4">
         <v>0.56657963446475201</v>
       </c>
-      <c r="AA62" s="6">
+      <c r="AA62" s="5">
         <v>0.48795180722891501</v>
       </c>
-      <c r="AB62" s="6">
+      <c r="AB62" s="5">
         <v>0.45578778135048198</v>
       </c>
-      <c r="AC62" s="6">
+      <c r="AC62" s="5">
         <v>0.42307692307692302</v>
       </c>
-      <c r="AD62" s="6">
+      <c r="AD62" s="5">
         <v>0.67460317460317398</v>
       </c>
-      <c r="AE62" s="6">
+      <c r="AE62" s="5">
         <v>0.59589041095890405</v>
       </c>
-      <c r="AF62" s="6">
+      <c r="AF62" s="5">
         <v>0.58288770053475902</v>
       </c>
-      <c r="AG62" s="6">
+      <c r="AG62" s="5">
         <v>0.50446428571428503</v>
       </c>
-      <c r="AH62" s="6">
+      <c r="AH62" s="5">
         <v>0.59533607681755796</v>
       </c>
-      <c r="AI62" s="6">
+      <c r="AI62" s="5">
         <v>0.30451127819548801</v>
       </c>
-      <c r="AJ62" s="6">
+      <c r="AJ62" s="5">
         <v>0.412964311726147</v>
       </c>
-      <c r="AK62" s="6">
+      <c r="AK62" s="5">
         <v>0.35483870967741898</v>
       </c>
-      <c r="AL62" s="6">
+      <c r="AL62" s="5">
         <v>0.76576576576576505</v>
       </c>
-      <c r="AM62" s="6">
+      <c r="AM62" s="5">
         <v>0.54037267080745299</v>
       </c>
-      <c r="AN62" s="5">
+      <c r="AN62" s="4">
         <v>0.59239130434782605</v>
       </c>
-      <c r="AO62" s="5">
+      <c r="AO62" s="4">
         <v>9.1968999999999994</v>
       </c>
-      <c r="AP62" s="5">
+      <c r="AP62" s="4">
         <v>197.459</v>
       </c>
-      <c r="AQ62" s="5">
+      <c r="AQ62" s="4">
         <v>12.396000000000001</v>
       </c>
     </row>
-    <row r="63" spans="1:43" s="5" customFormat="1" x14ac:dyDescent="0.45">
-      <c r="A63" s="5">
+    <row r="63" spans="1:43" s="4" customFormat="1" x14ac:dyDescent="0.45">
+      <c r="A63" s="4">
         <v>43</v>
       </c>
-      <c r="B63" s="5" t="s">
+      <c r="B63" s="4" t="s">
         <v>603</v>
       </c>
-      <c r="C63" s="5" t="s">
+      <c r="C63" s="4" t="s">
         <v>512</v>
       </c>
-      <c r="D63" s="5" t="s">
+      <c r="D63" s="4" t="s">
         <v>513</v>
       </c>
-      <c r="E63" s="6" t="s">
+      <c r="E63" s="5" t="s">
         <v>125</v>
       </c>
-      <c r="F63" s="5">
+      <c r="F63" s="4">
         <v>0.01</v>
       </c>
-      <c r="G63" s="5">
+      <c r="G63" s="4">
         <v>16</v>
       </c>
-      <c r="H63" s="5">
+      <c r="H63" s="4">
         <v>8</v>
       </c>
-      <c r="I63" s="5">
+      <c r="I63" s="4">
         <v>2</v>
       </c>
-      <c r="J63" s="5">
-        <v>400</v>
-      </c>
-      <c r="K63" s="5">
-        <v>400</v>
-      </c>
-      <c r="L63" s="6" t="s">
+      <c r="J63" s="4">
+        <v>400</v>
+      </c>
+      <c r="K63" s="4">
+        <v>400</v>
+      </c>
+      <c r="L63" s="5" t="s">
         <v>604</v>
       </c>
-      <c r="M63" s="5" t="s">
+      <c r="M63" s="4" t="s">
         <v>630</v>
       </c>
-      <c r="N63" s="5">
+      <c r="N63" s="4">
         <v>2000</v>
       </c>
-      <c r="O63" s="5" t="s">
+      <c r="O63" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="P63" s="6" t="s">
+      <c r="P63" s="5" t="s">
         <v>618</v>
       </c>
-      <c r="Q63" s="8">
+      <c r="Q63" s="7">
         <v>0.55246952368983204</v>
       </c>
-      <c r="R63" s="6" t="s">
+      <c r="R63" s="5" t="s">
         <v>619</v>
       </c>
-      <c r="S63" s="5">
+      <c r="S63" s="4">
         <v>0.37579617834394902</v>
       </c>
-      <c r="T63" s="6" t="s">
+      <c r="T63" s="5" t="s">
         <v>620</v>
       </c>
-      <c r="U63" s="6" t="s">
+      <c r="U63" s="5" t="s">
         <v>491</v>
       </c>
-      <c r="V63" s="6" t="s">
+      <c r="V63" s="5" t="s">
         <v>621</v>
       </c>
-      <c r="W63" s="6" t="s">
+      <c r="W63" s="5" t="s">
         <v>622</v>
       </c>
-      <c r="X63" s="6" t="s">
+      <c r="X63" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="Y63" s="6" t="s">
+      <c r="Y63" s="5" t="s">
         <v>624</v>
       </c>
-      <c r="Z63" s="6">
+      <c r="Z63" s="5">
         <v>0.61347743165924895</v>
       </c>
-      <c r="AA63" s="6">
+      <c r="AA63" s="5">
         <v>0.51754385964912197</v>
       </c>
-      <c r="AB63" s="6">
+      <c r="AB63" s="5">
         <v>0.49464524765729501</v>
       </c>
-      <c r="AC63" s="6">
+      <c r="AC63" s="5">
         <v>0.62686567164179097</v>
       </c>
-      <c r="AD63" s="6">
+      <c r="AD63" s="5">
         <v>0.79310344827586199</v>
       </c>
-      <c r="AE63" s="6">
+      <c r="AE63" s="5">
         <v>0.71770334928229595</v>
       </c>
-      <c r="AF63" s="6">
+      <c r="AF63" s="5">
         <v>0.72803347280334696</v>
       </c>
-      <c r="AG63" s="6">
+      <c r="AG63" s="5">
         <v>0.52659319597508303</v>
       </c>
-      <c r="AH63" s="6">
+      <c r="AH63" s="5">
         <v>0.58591378263509397</v>
       </c>
-      <c r="AI63" s="5">
+      <c r="AI63" s="4">
         <v>0.29499999999999998</v>
       </c>
-      <c r="AJ63" s="6">
+      <c r="AJ63" s="5">
         <v>0.44119402985074602</v>
       </c>
-      <c r="AK63" s="6">
+      <c r="AK63" s="5">
         <v>0.54545454545454497</v>
       </c>
-      <c r="AL63" s="5">
+      <c r="AL63" s="4">
         <v>0.69696969696969702</v>
       </c>
-      <c r="AM63" s="6">
+      <c r="AM63" s="5">
         <v>0.62761506276150603</v>
       </c>
-      <c r="AN63" s="6">
+      <c r="AN63" s="5">
         <v>0.734177215189873</v>
       </c>
-      <c r="AO63" s="5">
+      <c r="AO63" s="4">
         <v>7.8232999999999997</v>
       </c>
-      <c r="AP63" s="5">
+      <c r="AP63" s="4">
         <v>194.29</v>
       </c>
-      <c r="AQ63" s="5">
+      <c r="AQ63" s="4">
         <v>12.143000000000001</v>
       </c>
     </row>
     <row r="64" spans="1:43" x14ac:dyDescent="0.45">
-      <c r="Y64" s="5" t="s">
+      <c r="Y64" s="4" t="s">
         <v>23</v>
       </c>
       <c r="Z64" t="s">
@@ -11114,7 +11200,7 @@
       <c r="AF64" t="s">
         <v>30</v>
       </c>
-      <c r="AG64" s="5" t="s">
+      <c r="AG64" s="4" t="s">
         <v>31</v>
       </c>
       <c r="AH64" t="s">
@@ -11140,139 +11226,139 @@
       </c>
     </row>
     <row r="65" spans="24:40" x14ac:dyDescent="0.45">
-      <c r="X65" s="5" t="s">
+      <c r="X65" s="4" t="s">
         <v>634</v>
       </c>
-      <c r="Y65" s="5">
-        <f>AVERAGE(Y50:Y63)</f>
+      <c r="Y65" s="4">
+        <f t="shared" ref="Y65:AG65" si="0">AVERAGE(Y50:Y63)</f>
         <v>0.55461077526823277</v>
       </c>
-      <c r="Z65" s="5">
-        <f>AVERAGE(Z50:Z63)</f>
+      <c r="Z65" s="4">
+        <f t="shared" si="0"/>
         <v>0.5772222449496901</v>
       </c>
-      <c r="AA65" s="5">
-        <f>AVERAGE(AA50:AA63)</f>
+      <c r="AA65" s="4">
+        <f t="shared" si="0"/>
         <v>0.47995821956694901</v>
       </c>
-      <c r="AB65" s="5">
-        <f>AVERAGE(AB50:AB63)</f>
+      <c r="AB65" s="4">
+        <f t="shared" si="0"/>
         <v>0.47064386224162913</v>
       </c>
-      <c r="AC65" s="5">
-        <f>AVERAGE(AC50:AC63)</f>
+      <c r="AC65" s="4">
+        <f t="shared" si="0"/>
         <v>0.52584963586311362</v>
       </c>
-      <c r="AD65" s="5">
-        <f>AVERAGE(AD50:AD63)</f>
+      <c r="AD65" s="4">
+        <f t="shared" si="0"/>
         <v>0.73509613741128266</v>
       </c>
-      <c r="AE65" s="5">
-        <f>AVERAGE(AE50:AE63)</f>
+      <c r="AE65" s="4">
+        <f t="shared" si="0"/>
         <v>0.64388016872799902</v>
       </c>
-      <c r="AF65" s="5">
-        <f>AVERAGE(AF50:AF63)</f>
+      <c r="AF65" s="4">
+        <f t="shared" si="0"/>
         <v>0.67074516153091601</v>
       </c>
-      <c r="AG65" s="5">
-        <f>AVERAGE(AG50:AG63)</f>
+      <c r="AG65" s="4">
+        <f t="shared" si="0"/>
         <v>0.48803250411928012</v>
       </c>
-      <c r="AH65" s="5">
-        <f t="shared" ref="AH65:AN65" si="0">AVERAGE(AH50:AH63)</f>
+      <c r="AH65" s="4">
+        <f t="shared" ref="AH65:AN65" si="1">AVERAGE(AH50:AH63)</f>
         <v>0.57478162957822909</v>
       </c>
-      <c r="AI65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AI65" s="4">
+        <f t="shared" si="1"/>
         <v>0.25076530612244874</v>
       </c>
-      <c r="AJ65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AJ65" s="4">
+        <f t="shared" si="1"/>
         <v>0.3872828863693184</v>
       </c>
-      <c r="AK65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AK65" s="4">
+        <f t="shared" si="1"/>
         <v>0.4542462146148778</v>
       </c>
-      <c r="AL65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AL65" s="4">
+        <f t="shared" si="1"/>
         <v>0.72692172692172641</v>
       </c>
-      <c r="AM65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AM65" s="4">
+        <f t="shared" si="1"/>
         <v>0.54301047324514629</v>
       </c>
-      <c r="AN65" s="5">
-        <f t="shared" si="0"/>
+      <c r="AN65" s="4">
+        <f t="shared" si="1"/>
         <v>0.65644409937888171</v>
       </c>
     </row>
     <row r="66" spans="24:40" x14ac:dyDescent="0.45">
-      <c r="X66" s="5" t="s">
+      <c r="X66" s="4" t="s">
         <v>633</v>
       </c>
-      <c r="Y66" s="5">
-        <f>_xlfn.STDEV.S(Y50:Y63)</f>
+      <c r="Y66" s="4">
+        <f t="shared" ref="Y66:AG66" si="2">_xlfn.STDEV.S(Y50:Y63)</f>
         <v>2.4975054904913096E-2</v>
       </c>
-      <c r="Z66" s="5">
-        <f>_xlfn.STDEV.S(Z50:Z63)</f>
+      <c r="Z66" s="4">
+        <f t="shared" si="2"/>
         <v>3.4426604008229042E-2</v>
       </c>
-      <c r="AA66" s="5">
-        <f>_xlfn.STDEV.S(AA50:AA63)</f>
+      <c r="AA66" s="4">
+        <f t="shared" si="2"/>
         <v>5.5346704872731745E-2</v>
       </c>
-      <c r="AB66" s="5">
-        <f>_xlfn.STDEV.S(AB50:AB63)</f>
+      <c r="AB66" s="4">
+        <f t="shared" si="2"/>
         <v>1.9785465379435388E-2</v>
       </c>
-      <c r="AC66" s="5">
-        <f>_xlfn.STDEV.S(AC50:AC63)</f>
+      <c r="AC66" s="4">
+        <f t="shared" si="2"/>
         <v>9.9740919546641466E-2</v>
       </c>
-      <c r="AD66" s="5">
-        <f>_xlfn.STDEV.S(AD50:AD63)</f>
+      <c r="AD66" s="4">
+        <f t="shared" si="2"/>
         <v>4.7555267493801991E-2</v>
       </c>
-      <c r="AE66" s="5">
-        <f>_xlfn.STDEV.S(AE50:AE63)</f>
+      <c r="AE66" s="4">
+        <f t="shared" si="2"/>
         <v>8.6776104156993827E-2</v>
       </c>
-      <c r="AF66" s="5">
-        <f>_xlfn.STDEV.S(AF50:AF63)</f>
+      <c r="AF66" s="4">
+        <f t="shared" si="2"/>
         <v>6.3766196850905496E-2</v>
       </c>
-      <c r="AG66" s="5">
-        <f>_xlfn.STDEV.S(AG50:AG63)</f>
+      <c r="AG66" s="4">
+        <f t="shared" si="2"/>
         <v>3.1193341129330518E-2</v>
       </c>
-      <c r="AH66" s="5">
-        <f t="shared" ref="AH66:AN66" si="1">_xlfn.STDEV.S(AH50:AH63)</f>
+      <c r="AH66" s="4">
+        <f t="shared" ref="AH66:AM66" si="3">_xlfn.STDEV.S(AH50:AH63)</f>
         <v>1.7096845925819577E-2</v>
       </c>
-      <c r="AI66" s="5">
-        <f t="shared" si="1"/>
+      <c r="AI66" s="4">
+        <f t="shared" si="3"/>
         <v>4.6697255650003169E-2</v>
       </c>
-      <c r="AJ66" s="5">
-        <f t="shared" si="1"/>
+      <c r="AJ66" s="4">
+        <f t="shared" si="3"/>
         <v>4.2441214189673358E-2</v>
       </c>
-      <c r="AK66" s="5">
-        <f t="shared" si="1"/>
+      <c r="AK66" s="4">
+        <f t="shared" si="3"/>
         <v>8.5599211141321491E-2</v>
       </c>
-      <c r="AL66" s="5">
-        <f t="shared" si="1"/>
+      <c r="AL66" s="4">
+        <f t="shared" si="3"/>
         <v>7.0221178714280574E-2</v>
       </c>
-      <c r="AM66" s="5">
-        <f t="shared" si="1"/>
+      <c r="AM66" s="4">
+        <f t="shared" si="3"/>
         <v>7.2518681862493592E-2</v>
       </c>
-      <c r="AN66" s="5">
+      <c r="AN66" s="4">
         <f>_xlfn.STDEV.S(AN50:AN63)</f>
         <v>6.4616188924181819E-2</v>
       </c>
@@ -11288,6 +11374,1519 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5777E171-B9FE-4CE1-AA5B-8BA45B25FA78}">
+  <dimension ref="A1:AT14"/>
+  <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
+  <cols>
+    <col min="1" max="1" width="35.59765625" customWidth="1"/>
+    <col min="7" max="7" width="23.19921875" customWidth="1"/>
+    <col min="8" max="8" width="20.265625" customWidth="1"/>
+    <col min="9" max="9" width="15.59765625" customWidth="1"/>
+    <col min="10" max="10" width="22" customWidth="1"/>
+    <col min="11" max="11" width="20.265625" customWidth="1"/>
+    <col min="12" max="12" width="20.3984375" customWidth="1"/>
+    <col min="13" max="13" width="19.19921875" customWidth="1"/>
+    <col min="14" max="14" width="23.46484375" customWidth="1"/>
+    <col min="15" max="15" width="19.73046875" customWidth="1"/>
+    <col min="16" max="16" width="20.53125" customWidth="1"/>
+    <col min="17" max="17" width="20" customWidth="1"/>
+    <col min="18" max="18" width="20.3984375" customWidth="1"/>
+    <col min="19" max="19" width="17.73046875" customWidth="1"/>
+    <col min="20" max="20" width="22.53125" customWidth="1"/>
+    <col min="21" max="21" width="19.59765625" customWidth="1"/>
+    <col min="22" max="22" width="18.9296875" customWidth="1"/>
+    <col min="23" max="23" width="17.33203125" customWidth="1"/>
+    <col min="24" max="24" width="19.06640625" customWidth="1"/>
+    <col min="25" max="25" width="20.6640625" customWidth="1"/>
+    <col min="26" max="26" width="17.33203125" customWidth="1"/>
+    <col min="27" max="27" width="17.86328125" customWidth="1"/>
+    <col min="28" max="28" width="18.9296875" customWidth="1"/>
+    <col min="29" max="29" width="17.59765625" customWidth="1"/>
+    <col min="30" max="30" width="18.265625" customWidth="1"/>
+    <col min="31" max="31" width="27.19921875" customWidth="1"/>
+    <col min="32" max="32" width="26.3984375" customWidth="1"/>
+    <col min="33" max="33" width="20.53125" customWidth="1"/>
+    <col min="34" max="34" width="19.06640625" customWidth="1"/>
+    <col min="35" max="35" width="17.86328125" customWidth="1"/>
+    <col min="36" max="36" width="16" customWidth="1"/>
+    <col min="37" max="37" width="19.33203125" customWidth="1"/>
+    <col min="38" max="38" width="14.9296875" customWidth="1"/>
+    <col min="39" max="39" width="20.9296875" customWidth="1"/>
+    <col min="40" max="40" width="22.796875" customWidth="1"/>
+    <col min="41" max="41" width="19.59765625" customWidth="1"/>
+    <col min="42" max="42" width="16" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A1" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" t="s">
+        <v>12</v>
+      </c>
+      <c r="N1" t="s">
+        <v>13</v>
+      </c>
+      <c r="O1" t="s">
+        <v>14</v>
+      </c>
+      <c r="P1" t="s">
+        <v>635</v>
+      </c>
+      <c r="Q1" t="s">
+        <v>636</v>
+      </c>
+      <c r="R1" t="s">
+        <v>637</v>
+      </c>
+      <c r="S1" t="s">
+        <v>638</v>
+      </c>
+      <c r="T1" t="s">
+        <v>15</v>
+      </c>
+      <c r="U1" t="s">
+        <v>16</v>
+      </c>
+      <c r="V1" t="s">
+        <v>17</v>
+      </c>
+      <c r="W1" t="s">
+        <v>18</v>
+      </c>
+      <c r="X1" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y1" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z1" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA1" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB1" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC1" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD1" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE1" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF1" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG1" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH1" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI1" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ1" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK1" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL1" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM1" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN1" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO1" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP1" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ1" t="s">
+        <v>38</v>
+      </c>
+      <c r="AR1" t="s">
+        <v>39</v>
+      </c>
+      <c r="AS1" t="s">
+        <v>40</v>
+      </c>
+      <c r="AT1" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="2" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A2" t="s">
+        <v>644</v>
+      </c>
+      <c r="B2" t="s">
+        <v>639</v>
+      </c>
+      <c r="C2" t="s">
+        <v>645</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E2">
+        <v>0.01</v>
+      </c>
+      <c r="F2">
+        <v>16</v>
+      </c>
+      <c r="G2">
+        <v>8</v>
+      </c>
+      <c r="H2">
+        <v>4</v>
+      </c>
+      <c r="I2">
+        <v>400</v>
+      </c>
+      <c r="J2">
+        <v>400</v>
+      </c>
+      <c r="K2" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="L2" t="s">
+        <v>640</v>
+      </c>
+      <c r="M2">
+        <v>992</v>
+      </c>
+      <c r="N2" t="s">
+        <v>64</v>
+      </c>
+      <c r="O2" s="1" t="s">
+        <v>647</v>
+      </c>
+      <c r="S2">
+        <v>8</v>
+      </c>
+      <c r="T2" s="1">
+        <v>0.49192951280912101</v>
+      </c>
+      <c r="U2" s="1">
+        <v>0.53899670450384396</v>
+      </c>
+      <c r="V2" s="1">
+        <v>0.102325581395348</v>
+      </c>
+      <c r="W2" s="1">
+        <v>0.388931591083781</v>
+      </c>
+      <c r="X2" s="1">
+        <v>0.47058823529411697</v>
+      </c>
+      <c r="Y2" s="1">
+        <v>0.73033707865168496</v>
+      </c>
+      <c r="Z2" s="1">
+        <v>0.65573770491803196</v>
+      </c>
+      <c r="AA2" s="1">
+        <v>0.73706896551724099</v>
+      </c>
+      <c r="AB2" s="1">
+        <v>0.64032382420971401</v>
+      </c>
+      <c r="AC2" s="1">
+        <v>0.67461044912923895</v>
+      </c>
+      <c r="AD2" s="1">
+        <v>0.73333333333333295</v>
+      </c>
+      <c r="AE2" s="1">
+        <v>0.54175588865096302</v>
+      </c>
+      <c r="AF2" s="1">
+        <v>0.54237288135593198</v>
+      </c>
+      <c r="AG2" s="1">
+        <v>0.822784810126582</v>
+      </c>
+      <c r="AH2" s="1">
+        <v>0.74468085106382897</v>
+      </c>
+      <c r="AI2">
+        <v>0.75</v>
+      </c>
+      <c r="AJ2" s="1">
+        <v>0.39937484972349102</v>
+      </c>
+      <c r="AK2" s="1">
+        <v>0.448780487804878</v>
+      </c>
+      <c r="AL2">
+        <v>5.5E-2</v>
+      </c>
+      <c r="AM2" s="1">
+        <v>0.303357314148681</v>
+      </c>
+      <c r="AN2" s="1">
+        <v>0.415584415584415</v>
+      </c>
+      <c r="AO2" s="1">
+        <v>0.65656565656565602</v>
+      </c>
+      <c r="AP2" s="1">
+        <v>0.58577405857740505</v>
+      </c>
+      <c r="AQ2" s="1">
+        <v>0.72457627118643997</v>
+      </c>
+      <c r="AR2">
+        <v>7.2843999999999998</v>
+      </c>
+      <c r="AS2">
+        <v>207.01599999999999</v>
+      </c>
+      <c r="AT2">
+        <v>13.041</v>
+      </c>
+    </row>
+    <row r="3" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A3" t="s">
+        <v>644</v>
+      </c>
+      <c r="B3" t="s">
+        <v>639</v>
+      </c>
+      <c r="C3" t="s">
+        <v>645</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E3">
+        <v>0.01</v>
+      </c>
+      <c r="F3">
+        <v>16</v>
+      </c>
+      <c r="G3">
+        <v>8</v>
+      </c>
+      <c r="H3">
+        <v>4</v>
+      </c>
+      <c r="I3">
+        <v>400</v>
+      </c>
+      <c r="J3">
+        <v>400</v>
+      </c>
+      <c r="K3" s="1" t="s">
+        <v>646</v>
+      </c>
+      <c r="L3" t="s">
+        <v>640</v>
+      </c>
+      <c r="M3">
+        <v>992</v>
+      </c>
+      <c r="N3" t="s">
+        <v>46</v>
+      </c>
+      <c r="O3" s="1" t="s">
+        <v>648</v>
+      </c>
+      <c r="S3">
+        <v>8</v>
+      </c>
+      <c r="T3" s="1">
+        <v>0.45343432604579098</v>
+      </c>
+      <c r="U3" s="1">
+        <v>0.50749898662342896</v>
+      </c>
+      <c r="V3">
+        <v>9.0592334494773497E-2</v>
+      </c>
+      <c r="W3" s="1">
+        <v>0.35946462715105099</v>
+      </c>
+      <c r="X3" s="1">
+        <v>0.36734693877551</v>
+      </c>
+      <c r="Y3" s="1">
+        <v>0.76793248945147596</v>
+      </c>
+      <c r="Z3" s="1">
+        <v>0.56026058631921805</v>
+      </c>
+      <c r="AA3" s="1">
+        <v>0.62702702702702695</v>
+      </c>
+      <c r="AB3" s="1">
+        <v>0.57839262187088203</v>
+      </c>
+      <c r="AC3" s="1">
+        <v>0.60541586073500897</v>
+      </c>
+      <c r="AD3" s="1">
+        <v>0.61904761904761896</v>
+      </c>
+      <c r="AE3" s="1">
+        <v>0.50948509485094795</v>
+      </c>
+      <c r="AF3">
+        <v>0.5</v>
+      </c>
+      <c r="AG3" s="1">
+        <v>0.71653543307086598</v>
+      </c>
+      <c r="AH3" s="1">
+        <v>0.577181208053691</v>
+      </c>
+      <c r="AI3" s="1">
+        <v>0.61052631578947303</v>
+      </c>
+      <c r="AJ3" s="1">
+        <v>0.37287655719139201</v>
+      </c>
+      <c r="AK3" s="1">
+        <v>0.43684577808792702</v>
+      </c>
+      <c r="AL3">
+        <v>4.8872180451127803E-2</v>
+      </c>
+      <c r="AM3" s="1">
+        <v>0.27769571639586399</v>
+      </c>
+      <c r="AN3" s="1">
+        <v>0.29032258064516098</v>
+      </c>
+      <c r="AO3" s="1">
+        <v>0.82727272727272705</v>
+      </c>
+      <c r="AP3" s="1">
+        <v>0.544303797468354</v>
+      </c>
+      <c r="AQ3" s="1">
+        <v>0.64444444444444404</v>
+      </c>
+      <c r="AR3">
+        <v>8.4619</v>
+      </c>
+      <c r="AS3">
+        <v>211.654</v>
+      </c>
+      <c r="AT3">
+        <v>13.236000000000001</v>
+      </c>
+    </row>
+    <row r="4" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A4" t="s">
+        <v>649</v>
+      </c>
+      <c r="B4" t="s">
+        <v>639</v>
+      </c>
+      <c r="C4" t="s">
+        <v>645</v>
+      </c>
+      <c r="D4" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E4">
+        <v>0.01</v>
+      </c>
+      <c r="F4">
+        <v>16</v>
+      </c>
+      <c r="G4">
+        <v>8</v>
+      </c>
+      <c r="H4">
+        <v>4</v>
+      </c>
+      <c r="I4">
+        <v>400</v>
+      </c>
+      <c r="J4">
+        <v>400</v>
+      </c>
+      <c r="K4" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L4" t="s">
+        <v>641</v>
+      </c>
+      <c r="M4">
+        <v>992</v>
+      </c>
+      <c r="N4" t="s">
+        <v>64</v>
+      </c>
+      <c r="O4" s="1" t="s">
+        <v>651</v>
+      </c>
+      <c r="S4">
+        <v>8</v>
+      </c>
+      <c r="T4" s="1">
+        <v>0.48741248324147102</v>
+      </c>
+      <c r="U4" s="1">
+        <v>0.52639460876076305</v>
+      </c>
+      <c r="V4">
+        <v>9.3023255813953404E-2</v>
+      </c>
+      <c r="W4" s="1">
+        <v>0.38876058506543398</v>
+      </c>
+      <c r="X4" s="1">
+        <v>0.51428571428571401</v>
+      </c>
+      <c r="Y4" s="1">
+        <v>0.70454545454545403</v>
+      </c>
+      <c r="Z4" s="1">
+        <v>0.66206896551724104</v>
+      </c>
+      <c r="AA4" s="1">
+        <v>0.73640167364016695</v>
+      </c>
+      <c r="AB4" s="1">
+        <v>0.64056382145653801</v>
+      </c>
+      <c r="AC4" s="1">
+        <v>0.68186226964112495</v>
+      </c>
+      <c r="AD4" s="1">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AE4">
+        <v>0.543010752688172</v>
+      </c>
+      <c r="AF4" s="1">
+        <v>0.57142857142857095</v>
+      </c>
+      <c r="AG4" s="1">
+        <v>0.80519480519480502</v>
+      </c>
+      <c r="AH4" s="1">
+        <v>0.73469387755102</v>
+      </c>
+      <c r="AI4" s="1">
+        <v>0.72727272727272696</v>
+      </c>
+      <c r="AJ4" s="1">
+        <v>0.39336378937244498</v>
+      </c>
+      <c r="AK4" s="1">
+        <v>0.42865853658536501</v>
+      </c>
+      <c r="AL4">
+        <v>0.05</v>
+      </c>
+      <c r="AM4">
+        <v>0.30275779376498801</v>
+      </c>
+      <c r="AN4" s="1">
+        <v>0.46753246753246702</v>
+      </c>
+      <c r="AO4" s="1">
+        <v>0.62626262626262597</v>
+      </c>
+      <c r="AP4">
+        <v>0.60251046025104604</v>
+      </c>
+      <c r="AQ4" s="1">
+        <v>0.74576271186440601</v>
+      </c>
+      <c r="AR4">
+        <v>7.2927</v>
+      </c>
+      <c r="AS4">
+        <v>206.78299999999999</v>
+      </c>
+      <c r="AT4">
+        <v>13.026999999999999</v>
+      </c>
+    </row>
+    <row r="5" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A5" t="s">
+        <v>649</v>
+      </c>
+      <c r="B5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C5" t="s">
+        <v>645</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E5">
+        <v>0.01</v>
+      </c>
+      <c r="F5">
+        <v>16</v>
+      </c>
+      <c r="G5">
+        <v>8</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>400</v>
+      </c>
+      <c r="J5">
+        <v>400</v>
+      </c>
+      <c r="K5" s="1" t="s">
+        <v>650</v>
+      </c>
+      <c r="L5" t="s">
+        <v>641</v>
+      </c>
+      <c r="M5">
+        <v>992</v>
+      </c>
+      <c r="N5" t="s">
+        <v>46</v>
+      </c>
+      <c r="O5">
+        <v>0.51497989892959595</v>
+      </c>
+      <c r="S5">
+        <v>8</v>
+      </c>
+      <c r="T5" s="1">
+        <v>0.43577578632929098</v>
+      </c>
+      <c r="U5" s="1">
+        <v>0.48441449031171002</v>
+      </c>
+      <c r="V5">
+        <v>8.3916083916083906E-2</v>
+      </c>
+      <c r="W5" s="1">
+        <v>0.34015594541910299</v>
+      </c>
+      <c r="X5" s="1">
+        <v>0.37735849056603699</v>
+      </c>
+      <c r="Y5">
+        <v>0.77446808510638299</v>
+      </c>
+      <c r="Z5" s="1">
+        <v>0.54313099041533497</v>
+      </c>
+      <c r="AA5" s="1">
+        <v>0.62433862433862397</v>
+      </c>
+      <c r="AB5" s="1">
+        <v>0.57433997220935595</v>
+      </c>
+      <c r="AC5" s="1">
+        <v>0.61105207226354896</v>
+      </c>
+      <c r="AD5">
+        <v>0.6</v>
+      </c>
+      <c r="AE5">
+        <v>0.5</v>
+      </c>
+      <c r="AF5" s="1">
+        <v>0.45454545454545398</v>
+      </c>
+      <c r="AG5">
+        <v>0.72799999999999998</v>
+      </c>
+      <c r="AH5" s="1">
+        <v>0.54838709677419295</v>
+      </c>
+      <c r="AI5" s="1">
+        <v>0.59595959595959502</v>
+      </c>
+      <c r="AJ5" s="1">
+        <v>0.351075877689694</v>
+      </c>
+      <c r="AK5" s="1">
+        <v>0.40125610607117901</v>
+      </c>
+      <c r="AL5" s="1">
+        <v>4.5112781954887202E-2</v>
+      </c>
+      <c r="AM5" s="1">
+        <v>0.25775480059084099</v>
+      </c>
+      <c r="AN5" s="1">
+        <v>0.32258064516128998</v>
+      </c>
+      <c r="AO5" s="1">
+        <v>0.82727272727272705</v>
+      </c>
+      <c r="AP5" s="1">
+        <v>0.537974683544303</v>
+      </c>
+      <c r="AQ5" s="1">
+        <v>0.655555555555555</v>
+      </c>
+      <c r="AR5">
+        <v>8.4735999999999994</v>
+      </c>
+      <c r="AS5">
+        <v>211.36199999999999</v>
+      </c>
+      <c r="AT5">
+        <v>13.218</v>
+      </c>
+    </row>
+    <row r="6" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A6" t="s">
+        <v>652</v>
+      </c>
+      <c r="B6" t="s">
+        <v>639</v>
+      </c>
+      <c r="C6" t="s">
+        <v>645</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E6">
+        <v>0.01</v>
+      </c>
+      <c r="F6">
+        <v>16</v>
+      </c>
+      <c r="G6">
+        <v>8</v>
+      </c>
+      <c r="H6">
+        <v>4</v>
+      </c>
+      <c r="I6">
+        <v>400</v>
+      </c>
+      <c r="J6">
+        <v>400</v>
+      </c>
+      <c r="K6" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="L6" t="s">
+        <v>642</v>
+      </c>
+      <c r="M6">
+        <v>992</v>
+      </c>
+      <c r="N6" t="s">
+        <v>64</v>
+      </c>
+      <c r="O6" s="1" t="s">
+        <v>654</v>
+      </c>
+      <c r="S6">
+        <v>8</v>
+      </c>
+      <c r="T6" s="1">
+        <v>0.492098656033082</v>
+      </c>
+      <c r="U6" s="1">
+        <v>0.53923686105111501</v>
+      </c>
+      <c r="V6" s="1">
+        <v>2.8846153846153799E-2</v>
+      </c>
+      <c r="W6" s="1">
+        <v>0.390532544378698</v>
+      </c>
+      <c r="X6" s="1">
+        <v>0.50359712230215803</v>
+      </c>
+      <c r="Y6" s="1">
+        <v>0.70454545454545403</v>
+      </c>
+      <c r="Z6" s="1">
+        <v>0.66962305986696202</v>
+      </c>
+      <c r="AA6" s="1">
+        <v>0.70661157024793297</v>
+      </c>
+      <c r="AB6" s="1">
+        <v>0.63782542113323104</v>
+      </c>
+      <c r="AC6" s="1">
+        <v>0.65817223198593999</v>
+      </c>
+      <c r="AD6">
+        <v>0.375</v>
+      </c>
+      <c r="AE6" s="1">
+        <v>0.57093425605536297</v>
+      </c>
+      <c r="AF6" s="1">
+        <v>0.56451612903225801</v>
+      </c>
+      <c r="AG6" s="1">
+        <v>0.80519480519480502</v>
+      </c>
+      <c r="AH6" s="1">
+        <v>0.71226415094339601</v>
+      </c>
+      <c r="AI6" s="1">
+        <v>0.68951612903225801</v>
+      </c>
+      <c r="AJ6" s="1">
+        <v>0.40057706179370001</v>
+      </c>
+      <c r="AK6" s="1">
+        <v>0.45670731707317003</v>
+      </c>
+      <c r="AL6">
+        <v>1.4999999999999999E-2</v>
+      </c>
+      <c r="AM6" s="1">
+        <v>0.29676258992805699</v>
+      </c>
+      <c r="AN6" s="1">
+        <v>0.45454545454545398</v>
+      </c>
+      <c r="AO6" s="1">
+        <v>0.62626262626262597</v>
+      </c>
+      <c r="AP6" s="1">
+        <v>0.63179916317991602</v>
+      </c>
+      <c r="AQ6" s="1">
+        <v>0.72457627118643997</v>
+      </c>
+      <c r="AR6">
+        <v>7.4297000000000004</v>
+      </c>
+      <c r="AS6">
+        <v>202.96899999999999</v>
+      </c>
+      <c r="AT6">
+        <v>12.787000000000001</v>
+      </c>
+    </row>
+    <row r="7" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A7" t="s">
+        <v>652</v>
+      </c>
+      <c r="B7" t="s">
+        <v>639</v>
+      </c>
+      <c r="C7" t="s">
+        <v>645</v>
+      </c>
+      <c r="D7" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E7">
+        <v>0.01</v>
+      </c>
+      <c r="F7">
+        <v>16</v>
+      </c>
+      <c r="G7">
+        <v>8</v>
+      </c>
+      <c r="H7">
+        <v>4</v>
+      </c>
+      <c r="I7">
+        <v>400</v>
+      </c>
+      <c r="J7">
+        <v>400</v>
+      </c>
+      <c r="K7" s="1" t="s">
+        <v>653</v>
+      </c>
+      <c r="L7" t="s">
+        <v>642</v>
+      </c>
+      <c r="M7">
+        <v>992</v>
+      </c>
+      <c r="N7" t="s">
+        <v>46</v>
+      </c>
+      <c r="O7" s="1" t="s">
+        <v>655</v>
+      </c>
+      <c r="S7">
+        <v>8</v>
+      </c>
+      <c r="T7" s="1">
+        <v>0.44252972600379098</v>
+      </c>
+      <c r="U7" s="1">
+        <v>0.51364365971107495</v>
+      </c>
+      <c r="V7">
+        <v>2.2140221402214E-2</v>
+      </c>
+      <c r="W7" s="1">
+        <v>0.32055063913470899</v>
+      </c>
+      <c r="X7" s="1">
+        <v>0.39130434782608597</v>
+      </c>
+      <c r="Y7" s="1">
+        <v>0.76271186440677896</v>
+      </c>
+      <c r="Z7">
+        <v>0.54103343465045595</v>
+      </c>
+      <c r="AA7" s="1">
+        <v>0.64303797468354396</v>
+      </c>
+      <c r="AB7" s="1">
+        <v>0.56538969616908796</v>
+      </c>
+      <c r="AC7" s="1">
+        <v>0.60434372049102902</v>
+      </c>
+      <c r="AD7">
+        <v>0.6</v>
+      </c>
+      <c r="AE7" s="1">
+        <v>0.47941176470588198</v>
+      </c>
+      <c r="AF7">
+        <v>0.6</v>
+      </c>
+      <c r="AG7" s="1">
+        <v>0.71428571428571397</v>
+      </c>
+      <c r="AH7">
+        <v>0.52046783625730997</v>
+      </c>
+      <c r="AI7" s="1">
+        <v>0.59069767441860399</v>
+      </c>
+      <c r="AJ7" s="1">
+        <v>0.36353340883352198</v>
+      </c>
+      <c r="AK7" s="1">
+        <v>0.44661549197487699</v>
+      </c>
+      <c r="AL7" s="1">
+        <v>1.12781954887218E-2</v>
+      </c>
+      <c r="AM7" s="1">
+        <v>0.24076809453471101</v>
+      </c>
+      <c r="AN7" s="1">
+        <v>0.29032258064516098</v>
+      </c>
+      <c r="AO7" s="1">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="AP7" s="1">
+        <v>0.563291139240506</v>
+      </c>
+      <c r="AQ7" s="1">
+        <v>0.70555555555555505</v>
+      </c>
+      <c r="AR7">
+        <v>8.8012999999999995</v>
+      </c>
+      <c r="AS7">
+        <v>203.49199999999999</v>
+      </c>
+      <c r="AT7">
+        <v>12.725</v>
+      </c>
+    </row>
+    <row r="8" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A8" t="s">
+        <v>656</v>
+      </c>
+      <c r="B8" t="s">
+        <v>639</v>
+      </c>
+      <c r="C8" t="s">
+        <v>645</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E8">
+        <v>0.01</v>
+      </c>
+      <c r="F8">
+        <v>16</v>
+      </c>
+      <c r="G8">
+        <v>8</v>
+      </c>
+      <c r="H8">
+        <v>4</v>
+      </c>
+      <c r="I8">
+        <v>400</v>
+      </c>
+      <c r="J8">
+        <v>400</v>
+      </c>
+      <c r="K8" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L8" t="s">
+        <v>643</v>
+      </c>
+      <c r="M8">
+        <v>992</v>
+      </c>
+      <c r="N8" t="s">
+        <v>64</v>
+      </c>
+      <c r="O8">
+        <v>0.59960538148880005</v>
+      </c>
+      <c r="S8">
+        <v>8</v>
+      </c>
+      <c r="T8" s="1">
+        <v>0.50260869565217303</v>
+      </c>
+      <c r="U8" s="1">
+        <v>0.562870080111459</v>
+      </c>
+      <c r="V8">
+        <v>7.5471698113207503E-2</v>
+      </c>
+      <c r="W8" s="1">
+        <v>0.39103554868624402</v>
+      </c>
+      <c r="X8">
+        <v>0.5</v>
+      </c>
+      <c r="Y8" s="1">
+        <v>0.67777777777777704</v>
+      </c>
+      <c r="Z8" s="1">
+        <v>0.66216216216216195</v>
+      </c>
+      <c r="AA8">
+        <v>0.72117400419287203</v>
+      </c>
+      <c r="AB8" s="1">
+        <v>0.63261583363735796</v>
+      </c>
+      <c r="AC8" s="1">
+        <v>0.65637692932575098</v>
+      </c>
+      <c r="AD8" s="1">
+        <v>0.66666666666666596</v>
+      </c>
+      <c r="AE8">
+        <v>0.55000000000000004</v>
+      </c>
+      <c r="AF8" s="1">
+        <v>0.62745098039215597</v>
+      </c>
+      <c r="AG8" s="1">
+        <v>0.75308641975308599</v>
+      </c>
+      <c r="AH8" s="1">
+        <v>0.71707317073170695</v>
+      </c>
+      <c r="AI8" s="1">
+        <v>0.71369294605809097</v>
+      </c>
+      <c r="AJ8" s="1">
+        <v>0.41692714594854502</v>
+      </c>
+      <c r="AK8" s="1">
+        <v>0.49268292682926801</v>
+      </c>
+      <c r="AL8">
+        <v>0.04</v>
+      </c>
+      <c r="AM8" s="1">
+        <v>0.303357314148681</v>
+      </c>
+      <c r="AN8" s="1">
+        <v>0.415584415584415</v>
+      </c>
+      <c r="AO8" s="1">
+        <v>0.61616161616161602</v>
+      </c>
+      <c r="AP8" s="1">
+        <v>0.61506276150627603</v>
+      </c>
+      <c r="AQ8" s="1">
+        <v>0.72881355932203296</v>
+      </c>
+      <c r="AR8">
+        <v>7.4442000000000004</v>
+      </c>
+      <c r="AS8">
+        <v>202.57300000000001</v>
+      </c>
+      <c r="AT8">
+        <v>12.762</v>
+      </c>
+    </row>
+    <row r="9" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="A9" t="s">
+        <v>656</v>
+      </c>
+      <c r="B9" t="s">
+        <v>639</v>
+      </c>
+      <c r="C9" t="s">
+        <v>645</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>45</v>
+      </c>
+      <c r="E9">
+        <v>0.01</v>
+      </c>
+      <c r="F9">
+        <v>16</v>
+      </c>
+      <c r="G9">
+        <v>8</v>
+      </c>
+      <c r="H9">
+        <v>4</v>
+      </c>
+      <c r="I9">
+        <v>400</v>
+      </c>
+      <c r="J9">
+        <v>400</v>
+      </c>
+      <c r="K9" s="1" t="s">
+        <v>657</v>
+      </c>
+      <c r="L9" t="s">
+        <v>643</v>
+      </c>
+      <c r="M9">
+        <v>992</v>
+      </c>
+      <c r="N9" t="s">
+        <v>46</v>
+      </c>
+      <c r="O9" s="1" t="s">
+        <v>658</v>
+      </c>
+      <c r="S9">
+        <v>8</v>
+      </c>
+      <c r="T9" s="1">
+        <v>0.446634942216179</v>
+      </c>
+      <c r="U9" s="1">
+        <v>0.51166468960063205</v>
+      </c>
+      <c r="V9">
+        <v>6.3829787234042507E-2</v>
+      </c>
+      <c r="W9">
+        <v>0.33301158301158301</v>
+      </c>
+      <c r="X9" s="1">
+        <v>0.30434782608695599</v>
+      </c>
+      <c r="Y9" s="1">
+        <v>0.75313807531380705</v>
+      </c>
+      <c r="Z9" s="1">
+        <v>0.56790123456790098</v>
+      </c>
+      <c r="AA9" s="1">
+        <v>0.63265306122448906</v>
+      </c>
+      <c r="AB9" s="1">
+        <v>0.55867346938775497</v>
+      </c>
+      <c r="AC9" s="1">
+        <v>0.59032846715328402</v>
+      </c>
+      <c r="AD9">
+        <v>0.5625</v>
+      </c>
+      <c r="AE9" s="1">
+        <v>0.48050139275766002</v>
+      </c>
+      <c r="AF9" s="1">
+        <v>0.46666666666666601</v>
+      </c>
+      <c r="AG9" s="1">
+        <v>0.69767441860465096</v>
+      </c>
+      <c r="AH9" s="1">
+        <v>0.55421686746987897</v>
+      </c>
+      <c r="AI9" s="1">
+        <v>0.58490566037735803</v>
+      </c>
+      <c r="AJ9" s="1">
+        <v>0.37202718006794999</v>
+      </c>
+      <c r="AK9" s="1">
+        <v>0.451500348918353</v>
+      </c>
+      <c r="AL9">
+        <v>3.3834586466165398E-2</v>
+      </c>
+      <c r="AM9" s="1">
+        <v>0.254800590841949</v>
+      </c>
+      <c r="AN9" s="1">
+        <v>0.225806451612903</v>
+      </c>
+      <c r="AO9" s="1">
+        <v>0.81818181818181801</v>
+      </c>
+      <c r="AP9" s="1">
+        <v>0.582278481012658</v>
+      </c>
+      <c r="AQ9" s="1">
+        <v>0.688888888888888</v>
+      </c>
+      <c r="AR9">
+        <v>8.7025000000000006</v>
+      </c>
+      <c r="AS9">
+        <v>205.804</v>
+      </c>
+      <c r="AT9">
+        <v>12.87</v>
+      </c>
+    </row>
+    <row r="12" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="T12" t="s">
+        <v>15</v>
+      </c>
+      <c r="U12" t="s">
+        <v>16</v>
+      </c>
+      <c r="V12" t="s">
+        <v>17</v>
+      </c>
+      <c r="W12" t="s">
+        <v>18</v>
+      </c>
+      <c r="X12" t="s">
+        <v>19</v>
+      </c>
+      <c r="Y12" t="s">
+        <v>20</v>
+      </c>
+      <c r="Z12" t="s">
+        <v>21</v>
+      </c>
+      <c r="AA12" t="s">
+        <v>22</v>
+      </c>
+      <c r="AB12" t="s">
+        <v>23</v>
+      </c>
+      <c r="AC12" t="s">
+        <v>24</v>
+      </c>
+      <c r="AD12" t="s">
+        <v>25</v>
+      </c>
+      <c r="AE12" t="s">
+        <v>26</v>
+      </c>
+      <c r="AF12" t="s">
+        <v>27</v>
+      </c>
+      <c r="AG12" t="s">
+        <v>28</v>
+      </c>
+      <c r="AH12" t="s">
+        <v>29</v>
+      </c>
+      <c r="AI12" t="s">
+        <v>30</v>
+      </c>
+      <c r="AJ12" t="s">
+        <v>31</v>
+      </c>
+      <c r="AK12" t="s">
+        <v>32</v>
+      </c>
+      <c r="AL12" t="s">
+        <v>33</v>
+      </c>
+      <c r="AM12" t="s">
+        <v>34</v>
+      </c>
+      <c r="AN12" t="s">
+        <v>35</v>
+      </c>
+      <c r="AO12" t="s">
+        <v>36</v>
+      </c>
+      <c r="AP12" t="s">
+        <v>37</v>
+      </c>
+      <c r="AQ12" t="s">
+        <v>38</v>
+      </c>
+    </row>
+    <row r="13" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="S13" t="s">
+        <v>634</v>
+      </c>
+      <c r="T13">
+        <f>AVERAGE(T2:T9)</f>
+        <v>0.46905301604136235</v>
+      </c>
+      <c r="U13">
+        <f t="shared" ref="U13:AQ13" si="0">AVERAGE(U2:U9)</f>
+        <v>0.52309001008425338</v>
+      </c>
+      <c r="V13">
+        <f t="shared" si="0"/>
+        <v>7.0018139526972084E-2</v>
+      </c>
+      <c r="W13">
+        <f t="shared" si="0"/>
+        <v>0.36405538299132534</v>
+      </c>
+      <c r="X13">
+        <f t="shared" si="0"/>
+        <v>0.42860358439207225</v>
+      </c>
+      <c r="Y13">
+        <f t="shared" si="0"/>
+        <v>0.73443203497485188</v>
+      </c>
+      <c r="Z13">
+        <f t="shared" si="0"/>
+        <v>0.6077397673021635</v>
+      </c>
+      <c r="AA13">
+        <f t="shared" si="0"/>
+        <v>0.67853911260898714</v>
+      </c>
+      <c r="AB13">
+        <f t="shared" si="0"/>
+        <v>0.60351558250924031</v>
+      </c>
+      <c r="AC13">
+        <f t="shared" si="0"/>
+        <v>0.63527025009061577</v>
+      </c>
+      <c r="AD13">
+        <f t="shared" si="0"/>
+        <v>0.60290178571428554</v>
+      </c>
+      <c r="AE13">
+        <f t="shared" si="0"/>
+        <v>0.52188739371362347</v>
+      </c>
+      <c r="AF13">
+        <f t="shared" si="0"/>
+        <v>0.54087258542762962</v>
+      </c>
+      <c r="AG13">
+        <f t="shared" si="0"/>
+        <v>0.75534455077881357</v>
+      </c>
+      <c r="AH13">
+        <f t="shared" si="0"/>
+        <v>0.63862063235562816</v>
+      </c>
+      <c r="AI13">
+        <f t="shared" si="0"/>
+        <v>0.65782138111351329</v>
+      </c>
+      <c r="AJ13">
+        <f t="shared" si="0"/>
+        <v>0.38371948382759241</v>
+      </c>
+      <c r="AK13">
+        <f t="shared" si="0"/>
+        <v>0.44538087416812711</v>
+      </c>
+      <c r="AL13">
+        <f t="shared" si="0"/>
+        <v>3.7387218045112781E-2</v>
+      </c>
+      <c r="AM13">
+        <f t="shared" si="0"/>
+        <v>0.27965677679422152</v>
+      </c>
+      <c r="AN13">
+        <f t="shared" si="0"/>
+        <v>0.36028487641390822</v>
+      </c>
+      <c r="AO13">
+        <f t="shared" si="0"/>
+        <v>0.72702020202020179</v>
+      </c>
+      <c r="AP13">
+        <f t="shared" si="0"/>
+        <v>0.58287431809755796</v>
+      </c>
+      <c r="AQ13">
+        <f t="shared" si="0"/>
+        <v>0.70227165725047014</v>
+      </c>
+    </row>
+    <row r="14" spans="1:46" x14ac:dyDescent="0.45">
+      <c r="S14" t="s">
+        <v>633</v>
+      </c>
+      <c r="T14">
+        <f>_xlfn.STDEV.S(T2:T9)</f>
+        <v>2.6925457258206914E-2</v>
+      </c>
+      <c r="U14">
+        <f t="shared" ref="U14:AQ14" si="1">_xlfn.STDEV.S(U2:U9)</f>
+        <v>2.4100282728173016E-2</v>
+      </c>
+      <c r="V14">
+        <f t="shared" si="1"/>
+        <v>2.9868571601241487E-2</v>
+      </c>
+      <c r="W14">
+        <f t="shared" si="1"/>
+        <v>2.9536371199168653E-2</v>
+      </c>
+      <c r="X14">
+        <f t="shared" si="1"/>
+        <v>7.8408071722081946E-2</v>
+      </c>
+      <c r="Y14">
+        <f t="shared" si="1"/>
+        <v>3.5632487911822074E-2</v>
+      </c>
+      <c r="Z14">
+        <f t="shared" si="1"/>
+        <v>5.9175541447110042E-2</v>
+      </c>
+      <c r="AA14">
+        <f t="shared" si="1"/>
+        <v>5.1181281321843734E-2</v>
+      </c>
+      <c r="AB14">
+        <f t="shared" si="1"/>
+        <v>3.7221702606198281E-2</v>
+      </c>
+      <c r="AC14">
+        <f t="shared" si="1"/>
+        <v>3.6139568771603327E-2</v>
+      </c>
+      <c r="AD14">
+        <f t="shared" si="1"/>
+        <v>0.10622978165642048</v>
+      </c>
+      <c r="AE14">
+        <f t="shared" si="1"/>
+        <v>3.4198416585336802E-2</v>
+      </c>
+      <c r="AF14">
+        <f t="shared" si="1"/>
+        <v>6.2239475411209992E-2</v>
+      </c>
+      <c r="AG14">
+        <f t="shared" si="1"/>
+        <v>4.8973648513429703E-2</v>
+      </c>
+      <c r="AH14">
+        <f t="shared" si="1"/>
+        <v>9.6405378923185611E-2</v>
+      </c>
+      <c r="AI14">
+        <f t="shared" si="1"/>
+        <v>6.9005770023246191E-2</v>
+      </c>
+      <c r="AJ14">
+        <f t="shared" si="1"/>
+        <v>2.2208079417178443E-2</v>
+      </c>
+      <c r="AK14">
+        <f t="shared" si="1"/>
+        <v>2.595540604026363E-2</v>
+      </c>
+      <c r="AL14">
+        <f t="shared" si="1"/>
+        <v>1.6314749975548375E-2</v>
+      </c>
+      <c r="AM14">
+        <f t="shared" si="1"/>
+        <v>2.5532608498904097E-2</v>
+      </c>
+      <c r="AN14">
+        <f t="shared" si="1"/>
+        <v>8.928180258128568E-2</v>
+      </c>
+      <c r="AO14">
+        <f t="shared" si="1"/>
+        <v>0.10301155645312779</v>
+      </c>
+      <c r="AP14">
+        <f t="shared" si="1"/>
+        <v>3.3190448474424858E-2</v>
+      </c>
+      <c r="AQ14">
+        <f t="shared" si="1"/>
+        <v>3.6463678950537474E-2</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EA657019-E2CC-422E-AD15-376AEEA3A00E}">
   <dimension ref="A1:E11"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.45"/>
@@ -11323,11 +12922,11 @@
         <f>AVERAGE(combined_metrics!Q2:Q7)</f>
         <v>0.49953633133956782</v>
       </c>
-      <c r="D2" s="4">
+      <c r="D2" s="8">
         <f t="shared" ref="D2" si="0">AVERAGE(C2:C3)</f>
         <v>0.50050893578526245</v>
       </c>
-      <c r="E2" s="4">
+      <c r="E2" s="8">
         <f>_xlfn.STDEV.S(combined_metrics!Q2:Q13)</f>
         <v>3.1152026792491544E-2</v>
       </c>
@@ -11343,8 +12942,8 @@
         <f>AVERAGE(combined_metrics!Q8:Q13)</f>
         <v>0.50148154023095703</v>
       </c>
-      <c r="D3" s="4"/>
-      <c r="E3" s="4"/>
+      <c r="D3" s="8"/>
+      <c r="E3" s="8"/>
     </row>
     <row r="4" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A4" t="s">
@@ -11357,11 +12956,11 @@
         <f>AVERAGE(combined_metrics!Q14:Q19)</f>
         <v>0.49854497510491069</v>
       </c>
-      <c r="D4" s="4">
+      <c r="D4" s="8">
         <f t="shared" ref="D4" si="1">AVERAGE(C4:C5)</f>
         <v>0.4971318133159528</v>
       </c>
-      <c r="E4" s="4">
+      <c r="E4" s="8">
         <f>_xlfn.STDEV.S(combined_metrics!Q14:Q25)</f>
         <v>3.625733099248938E-2</v>
       </c>
@@ -11377,8 +12976,8 @@
         <f>AVERAGE(combined_metrics!Q20:Q25)</f>
         <v>0.49571865152699485</v>
       </c>
-      <c r="D5" s="4"/>
-      <c r="E5" s="4"/>
+      <c r="D5" s="8"/>
+      <c r="E5" s="8"/>
     </row>
     <row r="6" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A6" t="s">
@@ -11391,11 +12990,11 @@
         <f>AVERAGE(combined_metrics!Q26:Q31)</f>
         <v>0.48588761667003538</v>
       </c>
-      <c r="D6" s="4">
+      <c r="D6" s="8">
         <f t="shared" ref="D6" si="2">AVERAGE(C6:C7)</f>
         <v>0.49253501157301405</v>
       </c>
-      <c r="E6" s="4">
+      <c r="E6" s="8">
         <f>_xlfn.STDEV.S(combined_metrics!Q26:Q37)</f>
         <v>3.1010135296039302E-2</v>
       </c>
@@ -11411,8 +13010,8 @@
         <f>AVERAGE(combined_metrics!Q32:Q37)</f>
         <v>0.49918240647599266</v>
       </c>
-      <c r="D7" s="4"/>
-      <c r="E7" s="4"/>
+      <c r="D7" s="8"/>
+      <c r="E7" s="8"/>
     </row>
     <row r="8" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A8" t="s">
@@ -11425,11 +13024,11 @@
         <f>AVERAGE(combined_metrics!Q38:Q43)</f>
         <v>0.49672216369959016</v>
       </c>
-      <c r="D8" s="4">
+      <c r="D8" s="8">
         <f t="shared" ref="D8" si="3">AVERAGE(C8:C9)</f>
         <v>0.49551878060634752</v>
       </c>
-      <c r="E8" s="4">
+      <c r="E8" s="8">
         <f>_xlfn.STDEV.S(combined_metrics!Q38:Q49)</f>
         <v>3.1981225586452777E-2</v>
       </c>
@@ -11445,8 +13044,8 @@
         <f>AVERAGE(combined_metrics!Q44:Q49)</f>
         <v>0.49431539751310488</v>
       </c>
-      <c r="D9" s="4"/>
-      <c r="E9" s="4"/>
+      <c r="D9" s="8"/>
+      <c r="E9" s="8"/>
     </row>
     <row r="10" spans="1:5" x14ac:dyDescent="0.45">
       <c r="A10" t="s">
@@ -11459,11 +13058,11 @@
         <f>AVERAGE(combined_metrics!Q50:Q55)</f>
         <v>0.50344326605211009</v>
       </c>
-      <c r="D10" s="4">
+      <c r="D10" s="8">
         <f>AVERAGE(C10:C11)</f>
         <v>0.5131647306613607</v>
       </c>
-      <c r="E10" s="4">
+      <c r="E10" s="8">
         <f>_xlfn.STDEV.S(combined_metrics!Q50:Q63)</f>
         <v>2.8696665703877501E-2</v>
       </c>
@@ -11479,21 +13078,21 @@
         <f>AVERAGE(combined_metrics!Q56:Q61)</f>
         <v>0.52288619527061131</v>
       </c>
-      <c r="D11" s="4"/>
-      <c r="E11" s="4"/>
+      <c r="D11" s="8"/>
+      <c r="E11" s="8"/>
     </row>
   </sheetData>
   <mergeCells count="10">
+    <mergeCell ref="E2:E3"/>
+    <mergeCell ref="E4:E5"/>
+    <mergeCell ref="E6:E7"/>
+    <mergeCell ref="E8:E9"/>
+    <mergeCell ref="E10:E11"/>
     <mergeCell ref="D10:D11"/>
     <mergeCell ref="D8:D9"/>
     <mergeCell ref="D6:D7"/>
     <mergeCell ref="D4:D5"/>
     <mergeCell ref="D2:D3"/>
-    <mergeCell ref="E2:E3"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="E6:E7"/>
-    <mergeCell ref="E8:E9"/>
-    <mergeCell ref="E10:E11"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
